--- a/Financial Analysis/FI.xlsx
+++ b/Financial Analysis/FI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CD61B6-CC3D-416F-B22D-A0E993ED791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78E9E01-4AE3-4095-A264-A2448EEE8EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9F0C41CC-C0DB-440C-AB99-1B4D33A170AF}"/>
   </bookViews>
@@ -743,14 +743,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>176.85</v>
+        <v>161.83000000000001</v>
       </c>
       <c r="E3" s="3">
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45867</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>98045.64</v>
+        <v>89718.551999999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,7 +816,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>125165.64</v>
+        <v>116838.552</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>7134.2732297655002</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" ref="AF4:AJ4" si="2">AF4*1.02</f>
+        <f t="shared" ref="AG4:AJ4" si="2">AF4*1.02</f>
         <v>7276.9586943608101</v>
       </c>
       <c r="AH4" s="5">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AM31" s="4">
         <f>Main!D3</f>
-        <v>176.85</v>
+        <v>161.83000000000001</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AM32" s="10">
         <f>AM30/AM31-1</f>
-        <v>-0.57655076564752616</v>
+        <v>-0.53724898291271705</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FI.xlsx
+++ b/Financial Analysis/FI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78E9E01-4AE3-4095-A264-A2448EEE8EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C11E6F3-3A14-4312-A06A-32A696AA40CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9F0C41CC-C0DB-440C-AB99-1B4D33A170AF}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>FI</t>
   </si>
@@ -220,7 +220,10 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Q225 8K</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -320,14 +323,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -344,7 +347,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9982200" y="0"/>
+          <a:off x="10584180" y="0"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -743,17 +746,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>161.83000000000001</v>
+        <v>140.47999999999999</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45861</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45861</v>
       </c>
       <c r="G3" s="3">
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -761,11 +764,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>554.4</f>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -774,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>89718.551999999996</v>
+        <v>77643.296000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -782,11 +785,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>1177</f>
-        <v>1177</v>
+        <f>999</f>
+        <v>999</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -794,11 +797,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>1281+27016</f>
-        <v>28297</v>
+        <f>1528+28059</f>
+        <v>29587</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,7 +810,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-27120</v>
+        <v>-28588</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,7 +819,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>116838.552</v>
+        <v>106231.296</v>
       </c>
     </row>
   </sheetData>
@@ -961,6 +964,9 @@
       <c r="O3" s="5">
         <v>4045</v>
       </c>
+      <c r="P3" s="5">
+        <v>4304</v>
+      </c>
       <c r="T3" s="5">
         <v>8573</v>
       </c>
@@ -980,48 +986,48 @@
         <v>16637</v>
       </c>
       <c r="Z3" s="5">
-        <f>Y3*1.02</f>
-        <v>16969.740000000002</v>
+        <f>Y3*1.04</f>
+        <v>17302.48</v>
       </c>
       <c r="AA3" s="5">
-        <f t="shared" ref="AA3:AD3" si="0">Z3*1.02</f>
-        <v>17309.134800000003</v>
+        <f>Z3*1.03</f>
+        <v>17821.554400000001</v>
       </c>
       <c r="AB3" s="5">
-        <f t="shared" si="0"/>
-        <v>17655.317496000003</v>
+        <f t="shared" ref="AA3:AD3" si="0">AA3*1.02</f>
+        <v>18177.985488000002</v>
       </c>
       <c r="AC3" s="5">
         <f t="shared" si="0"/>
-        <v>18008.423845920002</v>
+        <v>18541.545197760002</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" si="0"/>
-        <v>18368.592322838402</v>
+        <v>18912.376101715203</v>
       </c>
       <c r="AE3" s="5">
         <f>AD3*1.01</f>
-        <v>18552.278246066788</v>
+        <v>19101.499862732355</v>
       </c>
       <c r="AF3" s="5">
         <f t="shared" ref="AF3:AJ3" si="1">AE3*1.01</f>
-        <v>18737.801028527454</v>
+        <v>19292.514861359679</v>
       </c>
       <c r="AG3" s="5">
         <f t="shared" si="1"/>
-        <v>18925.17903881273</v>
+        <v>19485.440009973277</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="1"/>
-        <v>19114.430829200857</v>
+        <v>19680.294410073009</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="1"/>
-        <v>19305.575137492866</v>
+        <v>19877.09735417374</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="1"/>
-        <v>19498.630888867796</v>
+        <v>20075.868327715478</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1050,6 +1056,9 @@
       <c r="O4" s="5">
         <v>1085</v>
       </c>
+      <c r="P4" s="5">
+        <v>1212</v>
+      </c>
       <c r="T4" s="5">
         <v>1614</v>
       </c>
@@ -1145,6 +1154,10 @@
         <f>O3+O4</f>
         <v>5130</v>
       </c>
+      <c r="P5" s="8">
+        <f>P3+P4</f>
+        <v>5516</v>
+      </c>
       <c r="T5" s="8">
         <f t="shared" ref="T5:Y5" si="3">T3+T4</f>
         <v>10187</v>
@@ -1171,47 +1184,47 @@
       </c>
       <c r="Z5" s="8">
         <f t="shared" ref="Z5:AJ5" si="4">Z3+Z4</f>
-        <v>21743.49</v>
+        <v>22076.23</v>
       </c>
       <c r="AA5" s="8">
         <f t="shared" si="4"/>
-        <v>22798.947300000003</v>
+        <v>23311.366900000001</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="4"/>
-        <v>23639.213121000004</v>
+        <v>24161.881113000003</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" si="4"/>
-        <v>24351.353208420001</v>
+        <v>24884.474560260001</v>
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="4"/>
-        <v>25028.668153463401</v>
+        <v>25572.451932340202</v>
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="4"/>
-        <v>25478.757109916787</v>
+        <v>26027.978726582354</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" si="4"/>
-        <v>25872.074258292952</v>
+        <v>26426.788091125178</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="4"/>
-        <v>26202.137733173542</v>
+        <v>26762.398704334089</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>26536.928697448886</v>
+        <v>27102.792278321038</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="4"/>
-        <v>26876.522963105854</v>
+        <v>27448.045179786728</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="4"/>
-        <v>27220.997670993042</v>
+        <v>27798.235109840723</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1240,6 +1253,9 @@
       <c r="O6" s="5">
         <v>1389</v>
       </c>
+      <c r="P6" s="5">
+        <v>1412</v>
+      </c>
       <c r="T6" s="5">
         <v>4016</v>
       </c>
@@ -1260,47 +1276,47 @@
       </c>
       <c r="Z6" s="5">
         <f>Z3*0.32</f>
-        <v>5430.3168000000005</v>
+        <v>5536.7936</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" ref="AA6:AJ6" si="6">AA3*0.32</f>
-        <v>5538.9231360000013</v>
+        <v>5702.8974080000007</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="6"/>
-        <v>5649.7015987200011</v>
+        <v>5816.9553561600005</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="6"/>
-        <v>5762.6956306944012</v>
+        <v>5933.2944632832005</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="6"/>
-        <v>5877.9495433082884</v>
+        <v>6051.9603525488646</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="6"/>
-        <v>5936.7290387413723</v>
+        <v>6112.479956074354</v>
       </c>
       <c r="AF6" s="5">
         <f t="shared" si="6"/>
-        <v>5996.0963291287853</v>
+        <v>6173.6047556350977</v>
       </c>
       <c r="AG6" s="5">
         <f t="shared" si="6"/>
-        <v>6056.0572924200742</v>
+        <v>6235.3408031914487</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" si="6"/>
-        <v>6116.6178653442748</v>
+        <v>6297.6942112233628</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="6"/>
-        <v>6177.7840439977172</v>
+        <v>6360.6711533355974</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="6"/>
-        <v>6239.561884437695</v>
+        <v>6424.2778648689527</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
@@ -1329,6 +1345,9 @@
       <c r="O7" s="5">
         <v>684</v>
       </c>
+      <c r="P7" s="5">
+        <v>694</v>
+      </c>
       <c r="T7" s="5">
         <v>1293</v>
       </c>
@@ -1424,6 +1443,10 @@
         <f>O6+O7</f>
         <v>2073</v>
       </c>
+      <c r="P8" s="5">
+        <f>P6+P7</f>
+        <v>2106</v>
+      </c>
       <c r="T8" s="5">
         <f t="shared" ref="T8:Z8" si="8">T6+T7</f>
         <v>5309</v>
@@ -1450,47 +1473,47 @@
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="8"/>
-        <v>8533.2543000000005</v>
+        <v>8639.7311000000009</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" ref="AA8:AJ8" si="9">AA6+AA7</f>
-        <v>9107.3012610000005</v>
+        <v>9271.275533</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="9"/>
-        <v>9539.2337549700023</v>
+        <v>9706.4875124099999</v>
       </c>
       <c r="AC8" s="5">
         <f t="shared" si="9"/>
-        <v>9885.5997163194006</v>
+        <v>10056.1985489082</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="9"/>
-        <v>10206.998833214539</v>
+        <v>10381.009642455116</v>
       </c>
       <c r="AE8" s="5">
         <f t="shared" si="9"/>
-        <v>10438.940300243874</v>
+        <v>10614.691217576856</v>
       </c>
       <c r="AF8" s="5">
         <f t="shared" si="9"/>
-        <v>10633.373928476361</v>
+        <v>10810.882354982674</v>
       </c>
       <c r="AG8" s="5">
         <f t="shared" si="9"/>
-        <v>10786.080443754601</v>
+        <v>10965.363954525976</v>
       </c>
       <c r="AH8" s="5">
         <f t="shared" si="9"/>
-        <v>10941.241479705492</v>
+        <v>11122.317825584581</v>
       </c>
       <c r="AI8" s="5">
         <f t="shared" si="9"/>
-        <v>11098.90013064616</v>
+        <v>11281.78723998404</v>
       </c>
       <c r="AJ8" s="5">
         <f t="shared" si="9"/>
-        <v>11259.100292819105</v>
+        <v>11443.816273250362</v>
       </c>
     </row>
     <row r="9" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1525,6 +1548,10 @@
         <f>O5-O8</f>
         <v>3057</v>
       </c>
+      <c r="P9" s="8">
+        <f>P5-P8</f>
+        <v>3410</v>
+      </c>
       <c r="T9" s="8">
         <f t="shared" ref="T9:Z9" si="10">T5-T8</f>
         <v>4878</v>
@@ -1551,47 +1578,47 @@
       </c>
       <c r="Z9" s="8">
         <f t="shared" si="10"/>
-        <v>13210.235700000001</v>
+        <v>13436.498899999999</v>
       </c>
       <c r="AA9" s="8">
         <f t="shared" ref="AA9:AJ9" si="11">AA5-AA8</f>
-        <v>13691.646039000003</v>
+        <v>14040.091367000001</v>
       </c>
       <c r="AB9" s="8">
         <f t="shared" si="11"/>
-        <v>14099.979366030002</v>
+        <v>14455.393600590003</v>
       </c>
       <c r="AC9" s="8">
         <f t="shared" si="11"/>
-        <v>14465.753492100601</v>
+        <v>14828.276011351802</v>
       </c>
       <c r="AD9" s="8">
         <f t="shared" si="11"/>
-        <v>14821.669320248862</v>
+        <v>15191.442289885086</v>
       </c>
       <c r="AE9" s="8">
         <f t="shared" si="11"/>
-        <v>15039.816809672913</v>
+        <v>15413.287509005499</v>
       </c>
       <c r="AF9" s="8">
         <f t="shared" si="11"/>
-        <v>15238.700329816591</v>
+        <v>15615.905736142504</v>
       </c>
       <c r="AG9" s="8">
         <f t="shared" si="11"/>
-        <v>15416.057289418941</v>
+        <v>15797.034749808114</v>
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="11"/>
-        <v>15595.687217743394</v>
+        <v>15980.474452736456</v>
       </c>
       <c r="AI9" s="8">
         <f t="shared" si="11"/>
-        <v>15777.622832459694</v>
+        <v>16166.257939802688</v>
       </c>
       <c r="AJ9" s="8">
         <f t="shared" si="11"/>
-        <v>15961.897378173937</v>
+        <v>16354.418836590361</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1620,6 +1647,9 @@
       <c r="O10" s="5">
         <v>1682</v>
       </c>
+      <c r="P10" s="5">
+        <v>1711</v>
+      </c>
       <c r="T10" s="5">
         <v>3284</v>
       </c>
@@ -1709,6 +1739,9 @@
       <c r="O11" s="5">
         <v>-20</v>
       </c>
+      <c r="P11" s="5">
+        <v>3</v>
+      </c>
       <c r="T11" s="5">
         <v>-15</v>
       </c>
@@ -1793,6 +1826,10 @@
         <f>SUM(O10:O11)</f>
         <v>1662</v>
       </c>
+      <c r="P12" s="5">
+        <f>SUM(P10:P11)</f>
+        <v>1714</v>
+      </c>
       <c r="T12" s="5">
         <f t="shared" ref="T12:Z12" si="14">SUM(T10:T11)</f>
         <v>3269</v>
@@ -1894,6 +1931,10 @@
         <f>O9-O12</f>
         <v>1395</v>
       </c>
+      <c r="P13" s="8">
+        <f>P9-P12</f>
+        <v>1696</v>
+      </c>
       <c r="T13" s="8">
         <f t="shared" ref="T13:Z13" si="16">T9-T12</f>
         <v>1609</v>
@@ -1920,47 +1961,47 @@
       </c>
       <c r="Z13" s="8">
         <f t="shared" si="16"/>
-        <v>6580.5957000000008</v>
+        <v>6806.8588999999984</v>
       </c>
       <c r="AA13" s="8">
         <f t="shared" ref="AA13:AJ13" si="17">AA9-AA12</f>
-        <v>6995.7096390000024</v>
+        <v>7344.1549670000004</v>
       </c>
       <c r="AB13" s="8">
         <f t="shared" si="17"/>
-        <v>7337.0836020300012</v>
+        <v>7692.4978365900024</v>
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="17"/>
-        <v>7635.2287704605997</v>
+        <v>7997.7512897118004</v>
       </c>
       <c r="AD13" s="8">
         <f t="shared" si="17"/>
-        <v>7922.8393513924611</v>
+        <v>8292.612321028686</v>
       </c>
       <c r="AE13" s="8">
         <f t="shared" si="17"/>
-        <v>8071.9985411279476</v>
+        <v>8445.4692404605339</v>
       </c>
       <c r="AF13" s="8">
         <f t="shared" si="17"/>
-        <v>8201.2038785861769</v>
+        <v>8578.4092849120898</v>
       </c>
       <c r="AG13" s="8">
         <f t="shared" si="17"/>
-        <v>8308.1858736762224</v>
+        <v>8689.1633340653934</v>
       </c>
       <c r="AH13" s="8">
         <f t="shared" si="17"/>
-        <v>8416.7370878432484</v>
+        <v>8801.5243228363106</v>
       </c>
       <c r="AI13" s="8">
         <f t="shared" si="17"/>
-        <v>8526.8832012605453</v>
+        <v>8915.5183086035395</v>
       </c>
       <c r="AJ13" s="8">
         <f t="shared" si="17"/>
-        <v>8638.6503506627978</v>
+        <v>9031.1718090792219</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
@@ -1989,6 +2030,9 @@
       <c r="O14" s="5">
         <v>331</v>
       </c>
+      <c r="P14" s="5">
+        <v>365</v>
+      </c>
       <c r="T14" s="5">
         <f>473+47</f>
         <v>520</v>
@@ -2079,6 +2123,9 @@
       <c r="O15" s="5">
         <v>18</v>
       </c>
+      <c r="P15" s="5">
+        <v>39</v>
+      </c>
       <c r="T15" s="5">
         <v>6</v>
       </c>
@@ -2174,6 +2221,10 @@
         <f>SUM(O14:O15)</f>
         <v>349</v>
       </c>
+      <c r="P16" s="5">
+        <f>SUM(P14:P15)</f>
+        <v>404</v>
+      </c>
       <c r="T16" s="5">
         <f t="shared" ref="T16:Z16" si="21">SUM(T14:T15)</f>
         <v>526</v>
@@ -2275,6 +2326,10 @@
         <f>O13-O16</f>
         <v>1046</v>
       </c>
+      <c r="P17" s="8">
+        <f>P13-P16</f>
+        <v>1292</v>
+      </c>
       <c r="T17" s="8">
         <f t="shared" ref="T17:Z17" si="23">T13-T16</f>
         <v>1083</v>
@@ -2301,47 +2356,47 @@
       </c>
       <c r="Z17" s="8">
         <f t="shared" si="23"/>
-        <v>5168.1857000000009</v>
+        <v>5394.4488999999985</v>
       </c>
       <c r="AA17" s="8">
         <f t="shared" ref="AA17:AJ17" si="24">AA13-AA16</f>
-        <v>5542.7429390000025</v>
+        <v>5891.1882670000005</v>
       </c>
       <c r="AB17" s="8">
         <f t="shared" si="24"/>
-        <v>5842.3798130300011</v>
+        <v>6197.7940475900023</v>
       </c>
       <c r="AC17" s="8">
         <f t="shared" si="24"/>
-        <v>6097.5728180305996</v>
+        <v>6460.0953372818003</v>
       </c>
       <c r="AD17" s="8">
         <f t="shared" si="24"/>
-        <v>6340.9804496343604</v>
+        <v>6710.7534192705862</v>
       </c>
       <c r="AE17" s="8">
         <f t="shared" si="24"/>
-        <v>6444.6491361467997</v>
+        <v>6818.1198354793869</v>
       </c>
       <c r="AF17" s="8">
         <f t="shared" si="24"/>
-        <v>6527.0385605618849</v>
+        <v>6904.2439668877978</v>
       </c>
       <c r="AG17" s="8">
         <f t="shared" si="24"/>
-        <v>6585.8402565996175</v>
+        <v>6966.8177169887886</v>
       </c>
       <c r="AH17" s="8">
         <f t="shared" si="24"/>
-        <v>6644.8066559525287</v>
+        <v>7029.5938909455908</v>
       </c>
       <c r="AI17" s="8">
         <f t="shared" si="24"/>
-        <v>6703.9221211852519</v>
+        <v>7092.557228528246</v>
       </c>
       <c r="AJ17" s="8">
         <f t="shared" si="24"/>
-        <v>6763.1702482528362</v>
+        <v>7155.6917066692604</v>
       </c>
     </row>
     <row r="18" spans="2:148" x14ac:dyDescent="0.3">
@@ -2370,6 +2425,9 @@
       <c r="O18" s="5">
         <v>190</v>
       </c>
+      <c r="P18" s="5">
+        <v>246</v>
+      </c>
       <c r="T18" s="5">
         <v>198</v>
       </c>
@@ -2390,47 +2448,47 @@
       </c>
       <c r="Z18" s="5">
         <f>Z17*0.18</f>
-        <v>930.27342600000009</v>
+        <v>971.00080199999968</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" ref="AA18:AJ18" si="26">AA17*0.18</f>
-        <v>997.69372902000043</v>
+        <v>1060.4138880600001</v>
       </c>
       <c r="AB18" s="5">
         <f t="shared" si="26"/>
-        <v>1051.6283663454001</v>
+        <v>1115.6029285662003</v>
       </c>
       <c r="AC18" s="5">
         <f t="shared" si="26"/>
-        <v>1097.5631072455078</v>
+        <v>1162.817160710724</v>
       </c>
       <c r="AD18" s="5">
         <f t="shared" si="26"/>
-        <v>1141.3764809341849</v>
+        <v>1207.9356154687055</v>
       </c>
       <c r="AE18" s="5">
         <f t="shared" si="26"/>
-        <v>1160.0368445064239</v>
+        <v>1227.2615703862896</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="26"/>
-        <v>1174.8669409011393</v>
+        <v>1242.7639140398035</v>
       </c>
       <c r="AG18" s="5">
         <f t="shared" si="26"/>
-        <v>1185.451246187931</v>
+        <v>1254.0271890579818</v>
       </c>
       <c r="AH18" s="5">
         <f t="shared" si="26"/>
-        <v>1196.0651980714551</v>
+        <v>1265.3269003702062</v>
       </c>
       <c r="AI18" s="5">
         <f t="shared" si="26"/>
-        <v>1206.7059818133453</v>
+        <v>1276.6603011350842</v>
       </c>
       <c r="AJ18" s="5">
         <f t="shared" si="26"/>
-        <v>1217.3706446855106</v>
+        <v>1288.0245072004668</v>
       </c>
     </row>
     <row r="19" spans="2:148" x14ac:dyDescent="0.3">
@@ -2465,6 +2523,10 @@
         <f>8-3</f>
         <v>5</v>
       </c>
+      <c r="P19" s="5">
+        <f>16+4</f>
+        <v>20</v>
+      </c>
       <c r="T19" s="5">
         <f>-29+21</f>
         <v>-8</v>
@@ -2490,47 +2552,47 @@
       </c>
       <c r="Z19" s="5">
         <f>Z17*0.02</f>
-        <v>103.36371400000002</v>
+        <v>107.88897799999997</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" ref="AA19:AJ19" si="27">AA17*0.02</f>
-        <v>110.85485878000006</v>
+        <v>117.82376534000001</v>
       </c>
       <c r="AB19" s="5">
         <f t="shared" si="27"/>
-        <v>116.84759626060003</v>
+        <v>123.95588095180005</v>
       </c>
       <c r="AC19" s="5">
         <f t="shared" si="27"/>
-        <v>121.951456360612</v>
+        <v>129.20190674563599</v>
       </c>
       <c r="AD19" s="5">
         <f t="shared" si="27"/>
-        <v>126.81960899268721</v>
+        <v>134.21506838541171</v>
       </c>
       <c r="AE19" s="5">
         <f t="shared" si="27"/>
-        <v>128.89298272293598</v>
+        <v>136.36239670958773</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="27"/>
-        <v>130.54077121123771</v>
+        <v>138.08487933775595</v>
       </c>
       <c r="AG19" s="5">
         <f t="shared" si="27"/>
-        <v>131.71680513199234</v>
+        <v>139.33635433977577</v>
       </c>
       <c r="AH19" s="5">
         <f t="shared" si="27"/>
-        <v>132.89613311905057</v>
+        <v>140.59187781891183</v>
       </c>
       <c r="AI19" s="5">
         <f t="shared" si="27"/>
-        <v>134.07844242370504</v>
+        <v>141.85114457056491</v>
       </c>
       <c r="AJ19" s="5">
         <f t="shared" si="27"/>
-        <v>135.26340496505674</v>
+        <v>143.11383413338521</v>
       </c>
     </row>
     <row r="20" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2565,6 +2627,10 @@
         <f>O17-O18-O19</f>
         <v>851</v>
       </c>
+      <c r="P20" s="8">
+        <f>P17-P18-P19</f>
+        <v>1026</v>
+      </c>
       <c r="T20" s="8">
         <f t="shared" ref="T20:Z20" si="28">T17-T18-T19</f>
         <v>893</v>
@@ -2591,495 +2657,495 @@
       </c>
       <c r="Z20" s="8">
         <f t="shared" si="28"/>
-        <v>4134.5485600000011</v>
+        <v>4315.559119999999</v>
       </c>
       <c r="AA20" s="8">
         <f t="shared" ref="AA20:AJ20" si="29">AA17-AA18-AA19</f>
-        <v>4434.1943512000025</v>
+        <v>4712.9506136</v>
       </c>
       <c r="AB20" s="8">
         <f t="shared" si="29"/>
-        <v>4673.9038504240007</v>
+        <v>4958.2352380720022</v>
       </c>
       <c r="AC20" s="8">
         <f t="shared" si="29"/>
-        <v>4878.0582544244799</v>
+        <v>5168.0762698254402</v>
       </c>
       <c r="AD20" s="8">
         <f t="shared" si="29"/>
-        <v>5072.7843597074889</v>
+        <v>5368.6027354164689</v>
       </c>
       <c r="AE20" s="8">
         <f t="shared" si="29"/>
-        <v>5155.7193089174398</v>
+        <v>5454.4958683835102</v>
       </c>
       <c r="AF20" s="8">
         <f t="shared" si="29"/>
-        <v>5221.6308484495084</v>
+        <v>5523.3951735102382</v>
       </c>
       <c r="AG20" s="8">
         <f t="shared" si="29"/>
-        <v>5268.672205279694</v>
+        <v>5573.4541735910316</v>
       </c>
       <c r="AH20" s="8">
         <f t="shared" si="29"/>
-        <v>5315.8453247620228</v>
+        <v>5623.675112756473</v>
       </c>
       <c r="AI20" s="8">
         <f t="shared" si="29"/>
-        <v>5363.1376969482017</v>
+        <v>5674.0457828225963</v>
       </c>
       <c r="AJ20" s="8">
         <f t="shared" si="29"/>
-        <v>5410.536198602269</v>
+        <v>5724.5533653354078</v>
       </c>
       <c r="AK20" s="1">
         <f>AJ20*(1+$AM$25)</f>
-        <v>5356.4308366162459</v>
+        <v>5667.3078316820538</v>
       </c>
       <c r="AL20" s="1">
         <f t="shared" ref="AL20:CW20" si="30">AK20*(1+$AM$25)</f>
-        <v>5302.8665282500833</v>
+        <v>5610.6347533652333</v>
       </c>
       <c r="AM20" s="1">
         <f t="shared" si="30"/>
-        <v>5249.8378629675826</v>
+        <v>5554.528405831581</v>
       </c>
       <c r="AN20" s="1">
         <f t="shared" si="30"/>
-        <v>5197.3394843379065</v>
+        <v>5498.9831217732653</v>
       </c>
       <c r="AO20" s="1">
         <f t="shared" si="30"/>
-        <v>5145.3660894945269</v>
+        <v>5443.9932905555324</v>
       </c>
       <c r="AP20" s="1">
         <f t="shared" si="30"/>
-        <v>5093.9124285995813</v>
+        <v>5389.5533576499774</v>
       </c>
       <c r="AQ20" s="1">
         <f t="shared" si="30"/>
-        <v>5042.9733043135857</v>
+        <v>5335.657824073478</v>
       </c>
       <c r="AR20" s="1">
         <f t="shared" si="30"/>
-        <v>4992.5435712704502</v>
+        <v>5282.301245832743</v>
       </c>
       <c r="AS20" s="1">
         <f t="shared" si="30"/>
-        <v>4942.6181355577455</v>
+        <v>5229.4782333744151</v>
       </c>
       <c r="AT20" s="1">
         <f t="shared" si="30"/>
-        <v>4893.1919542021678</v>
+        <v>5177.1834510406707</v>
       </c>
       <c r="AU20" s="1">
         <f t="shared" si="30"/>
-        <v>4844.2600346601457</v>
+        <v>5125.4116165302639</v>
       </c>
       <c r="AV20" s="1">
         <f t="shared" si="30"/>
-        <v>4795.8174343135443</v>
+        <v>5074.1575003649614</v>
       </c>
       <c r="AW20" s="1">
         <f t="shared" si="30"/>
-        <v>4747.8592599704089</v>
+        <v>5023.4159253613116</v>
       </c>
       <c r="AX20" s="1">
         <f t="shared" si="30"/>
-        <v>4700.3806673707049</v>
+        <v>4973.1817661076984</v>
       </c>
       <c r="AY20" s="1">
         <f t="shared" si="30"/>
-        <v>4653.3768606969979</v>
+        <v>4923.4499484466214</v>
       </c>
       <c r="AZ20" s="1">
         <f t="shared" si="30"/>
-        <v>4606.8430920900282</v>
+        <v>4874.2154489621553</v>
       </c>
       <c r="BA20" s="1">
         <f t="shared" si="30"/>
-        <v>4560.7746611691282</v>
+        <v>4825.4732944725338</v>
       </c>
       <c r="BB20" s="1">
         <f t="shared" si="30"/>
-        <v>4515.1669145574369</v>
+        <v>4777.2185615278086</v>
       </c>
       <c r="BC20" s="1">
         <f t="shared" si="30"/>
-        <v>4470.0152454118625</v>
+        <v>4729.4463759125301</v>
       </c>
       <c r="BD20" s="1">
         <f t="shared" si="30"/>
-        <v>4425.3150929577441</v>
+        <v>4682.1519121534047</v>
       </c>
       <c r="BE20" s="1">
         <f t="shared" si="30"/>
-        <v>4381.0619420281664</v>
+        <v>4635.3303930318707</v>
       </c>
       <c r="BF20" s="1">
         <f t="shared" si="30"/>
-        <v>4337.2513226078845</v>
+        <v>4588.9770891015523</v>
       </c>
       <c r="BG20" s="1">
         <f t="shared" si="30"/>
-        <v>4293.8788093818057</v>
+        <v>4543.087318210537</v>
       </c>
       <c r="BH20" s="1">
         <f t="shared" si="30"/>
-        <v>4250.9400212879873</v>
+        <v>4497.6564450284313</v>
       </c>
       <c r="BI20" s="1">
         <f t="shared" si="30"/>
-        <v>4208.4306210751074</v>
+        <v>4452.6798805781473</v>
       </c>
       <c r="BJ20" s="1">
         <f t="shared" si="30"/>
-        <v>4166.3463148643559</v>
+        <v>4408.153081772366</v>
       </c>
       <c r="BK20" s="1">
         <f t="shared" si="30"/>
-        <v>4124.6828517157119</v>
+        <v>4364.0715509546426</v>
       </c>
       <c r="BL20" s="1">
         <f t="shared" si="30"/>
-        <v>4083.4360231985547</v>
+        <v>4320.4308354450959</v>
       </c>
       <c r="BM20" s="1">
         <f t="shared" si="30"/>
-        <v>4042.6016629665692</v>
+        <v>4277.2265270906446</v>
       </c>
       <c r="BN20" s="1">
         <f t="shared" si="30"/>
-        <v>4002.1756463369034</v>
+        <v>4234.4542618197383</v>
       </c>
       <c r="BO20" s="1">
         <f t="shared" si="30"/>
-        <v>3962.1538898735344</v>
+        <v>4192.1097192015413</v>
       </c>
       <c r="BP20" s="1">
         <f t="shared" si="30"/>
-        <v>3922.5323509747991</v>
+        <v>4150.1886220095257</v>
       </c>
       <c r="BQ20" s="1">
         <f t="shared" si="30"/>
-        <v>3883.3070274650509</v>
+        <v>4108.6867357894307</v>
       </c>
       <c r="BR20" s="1">
         <f t="shared" si="30"/>
-        <v>3844.4739571904001</v>
+        <v>4067.5998684315364</v>
       </c>
       <c r="BS20" s="1">
         <f t="shared" si="30"/>
-        <v>3806.0292176184962</v>
+        <v>4026.923869747221</v>
       </c>
       <c r="BT20" s="1">
         <f t="shared" si="30"/>
-        <v>3767.968925442311</v>
+        <v>3986.6546310497488</v>
       </c>
       <c r="BU20" s="1">
         <f t="shared" si="30"/>
-        <v>3730.289236187888</v>
+        <v>3946.7880847392512</v>
       </c>
       <c r="BV20" s="1">
         <f t="shared" si="30"/>
-        <v>3692.986343826009</v>
+        <v>3907.3202038918585</v>
       </c>
       <c r="BW20" s="1">
         <f t="shared" si="30"/>
-        <v>3656.0564803877487</v>
+        <v>3868.2470018529398</v>
       </c>
       <c r="BX20" s="1">
         <f t="shared" si="30"/>
-        <v>3619.495915583871</v>
+        <v>3829.5645318344104</v>
       </c>
       <c r="BY20" s="1">
         <f t="shared" si="30"/>
-        <v>3583.3009564280324</v>
+        <v>3791.2688865160662</v>
       </c>
       <c r="BZ20" s="1">
         <f t="shared" si="30"/>
-        <v>3547.4679468637519</v>
+        <v>3753.3561976509054</v>
       </c>
       <c r="CA20" s="1">
         <f t="shared" si="30"/>
-        <v>3511.9932673951143</v>
+        <v>3715.8226356743962</v>
       </c>
       <c r="CB20" s="1">
         <f t="shared" si="30"/>
-        <v>3476.8733347211632</v>
+        <v>3678.6644093176524</v>
       </c>
       <c r="CC20" s="1">
         <f t="shared" si="30"/>
-        <v>3442.1046013739515</v>
+        <v>3641.8777652244758</v>
       </c>
       <c r="CD20" s="1">
         <f t="shared" si="30"/>
-        <v>3407.6835553602118</v>
+        <v>3605.4589875722309</v>
       </c>
       <c r="CE20" s="1">
         <f t="shared" si="30"/>
-        <v>3373.6067198066098</v>
+        <v>3569.4043976965086</v>
       </c>
       <c r="CF20" s="1">
         <f t="shared" si="30"/>
-        <v>3339.8706526085439</v>
+        <v>3533.7103537195435</v>
       </c>
       <c r="CG20" s="1">
         <f t="shared" si="30"/>
-        <v>3306.4719460824585</v>
+        <v>3498.3732501823479</v>
       </c>
       <c r="CH20" s="1">
         <f t="shared" si="30"/>
-        <v>3273.407226621634</v>
+        <v>3463.3895176805245</v>
       </c>
       <c r="CI20" s="1">
         <f t="shared" si="30"/>
-        <v>3240.6731543554174</v>
+        <v>3428.7556225037192</v>
       </c>
       <c r="CJ20" s="1">
         <f t="shared" si="30"/>
-        <v>3208.2664228118633</v>
+        <v>3394.4680662786818</v>
       </c>
       <c r="CK20" s="1">
         <f t="shared" si="30"/>
-        <v>3176.1837585837447</v>
+        <v>3360.5233856158948</v>
       </c>
       <c r="CL20" s="1">
         <f t="shared" si="30"/>
-        <v>3144.4219209979074</v>
+        <v>3326.9181517597358</v>
       </c>
       <c r="CM20" s="1">
         <f t="shared" si="30"/>
-        <v>3112.9777017879283</v>
+        <v>3293.6489702421386</v>
       </c>
       <c r="CN20" s="1">
         <f t="shared" si="30"/>
-        <v>3081.8479247700488</v>
+        <v>3260.712480539717</v>
       </c>
       <c r="CO20" s="1">
         <f t="shared" si="30"/>
-        <v>3051.0294455223484</v>
+        <v>3228.1053557343198</v>
       </c>
       <c r="CP20" s="1">
         <f t="shared" si="30"/>
-        <v>3020.5191510671248</v>
+        <v>3195.8243021769767</v>
       </c>
       <c r="CQ20" s="1">
         <f t="shared" si="30"/>
-        <v>2990.3139595564535</v>
+        <v>3163.866059155207</v>
       </c>
       <c r="CR20" s="1">
         <f t="shared" si="30"/>
-        <v>2960.4108199608891</v>
+        <v>3132.2273985636548</v>
       </c>
       <c r="CS20" s="1">
         <f t="shared" si="30"/>
-        <v>2930.80671176128</v>
+        <v>3100.9051245780183</v>
       </c>
       <c r="CT20" s="1">
         <f t="shared" si="30"/>
-        <v>2901.4986446436674</v>
+        <v>3069.8960733322383</v>
       </c>
       <c r="CU20" s="1">
         <f t="shared" si="30"/>
-        <v>2872.4836581972309</v>
+        <v>3039.1971125989157</v>
       </c>
       <c r="CV20" s="1">
         <f t="shared" si="30"/>
-        <v>2843.7588216152585</v>
+        <v>3008.8051414729266</v>
       </c>
       <c r="CW20" s="1">
         <f t="shared" si="30"/>
-        <v>2815.3212333991059</v>
+        <v>2978.7170900581973</v>
       </c>
       <c r="CX20" s="1">
         <f t="shared" ref="CX20:ER20" si="31">CW20*(1+$AM$25)</f>
-        <v>2787.1680210651148</v>
+        <v>2948.9299191576151</v>
       </c>
       <c r="CY20" s="1">
         <f t="shared" si="31"/>
-        <v>2759.2963408544638</v>
+        <v>2919.4406199660389</v>
       </c>
       <c r="CZ20" s="1">
         <f t="shared" si="31"/>
-        <v>2731.7033774459192</v>
+        <v>2890.2462137663783</v>
       </c>
       <c r="DA20" s="1">
         <f t="shared" si="31"/>
-        <v>2704.3863436714601</v>
+        <v>2861.3437516287145</v>
       </c>
       <c r="DB20" s="1">
         <f t="shared" si="31"/>
-        <v>2677.3424802347454</v>
+        <v>2832.7303141124271</v>
       </c>
       <c r="DC20" s="1">
         <f t="shared" si="31"/>
-        <v>2650.5690554323978</v>
+        <v>2804.4030109713026</v>
       </c>
       <c r="DD20" s="1">
         <f t="shared" si="31"/>
-        <v>2624.063364878074</v>
+        <v>2776.3589808615893</v>
       </c>
       <c r="DE20" s="1">
         <f t="shared" si="31"/>
-        <v>2597.8227312292934</v>
+        <v>2748.5953910529734</v>
       </c>
       <c r="DF20" s="1">
         <f t="shared" si="31"/>
-        <v>2571.8445039170006</v>
+        <v>2721.1094371424438</v>
       </c>
       <c r="DG20" s="1">
         <f t="shared" si="31"/>
-        <v>2546.1260588778305</v>
+        <v>2693.8983427710191</v>
       </c>
       <c r="DH20" s="1">
         <f t="shared" si="31"/>
-        <v>2520.6647982890522</v>
+        <v>2666.9593593433087</v>
       </c>
       <c r="DI20" s="1">
         <f t="shared" si="31"/>
-        <v>2495.4581503061618</v>
+        <v>2640.2897657498756</v>
       </c>
       <c r="DJ20" s="1">
         <f t="shared" si="31"/>
-        <v>2470.5035688031003</v>
+        <v>2613.886868092377</v>
       </c>
       <c r="DK20" s="1">
         <f t="shared" si="31"/>
-        <v>2445.7985331150694</v>
+        <v>2587.7479994114533</v>
       </c>
       <c r="DL20" s="1">
         <f t="shared" si="31"/>
-        <v>2421.3405477839187</v>
+        <v>2561.8705194173385</v>
       </c>
       <c r="DM20" s="1">
         <f t="shared" si="31"/>
-        <v>2397.1271423060793</v>
+        <v>2536.2518142231652</v>
       </c>
       <c r="DN20" s="1">
         <f t="shared" si="31"/>
-        <v>2373.1558708830185</v>
+        <v>2510.8892960809335</v>
       </c>
       <c r="DO20" s="1">
         <f t="shared" si="31"/>
-        <v>2349.4243121741883</v>
+        <v>2485.780403120124</v>
       </c>
       <c r="DP20" s="1">
         <f t="shared" si="31"/>
-        <v>2325.9300690524465</v>
+        <v>2460.9225990889227</v>
       </c>
       <c r="DQ20" s="1">
         <f t="shared" si="31"/>
-        <v>2302.670768361922</v>
+        <v>2436.3133730980335</v>
       </c>
       <c r="DR20" s="1">
         <f t="shared" si="31"/>
-        <v>2279.6440606783026</v>
+        <v>2411.9502393670532</v>
       </c>
       <c r="DS20" s="1">
         <f t="shared" si="31"/>
-        <v>2256.8476200715195</v>
+        <v>2387.8307369733825</v>
       </c>
       <c r="DT20" s="1">
         <f t="shared" si="31"/>
-        <v>2234.2791438708041</v>
+        <v>2363.9524296036489</v>
       </c>
       <c r="DU20" s="1">
         <f t="shared" si="31"/>
-        <v>2211.9363524320961</v>
+        <v>2340.3129053076123</v>
       </c>
       <c r="DV20" s="1">
         <f t="shared" si="31"/>
-        <v>2189.8169889077753</v>
+        <v>2316.9097762545362</v>
       </c>
       <c r="DW20" s="1">
         <f t="shared" si="31"/>
-        <v>2167.9188190186974</v>
+        <v>2293.7406784919908</v>
       </c>
       <c r="DX20" s="1">
         <f t="shared" si="31"/>
-        <v>2146.2396308285106</v>
+        <v>2270.803271707071</v>
       </c>
       <c r="DY20" s="1">
         <f t="shared" si="31"/>
-        <v>2124.7772345202256</v>
+        <v>2248.0952389900003</v>
       </c>
       <c r="DZ20" s="1">
         <f t="shared" si="31"/>
-        <v>2103.5294621750236</v>
+        <v>2225.6142866001005</v>
       </c>
       <c r="EA20" s="1">
         <f t="shared" si="31"/>
-        <v>2082.4941675532732</v>
+        <v>2203.3581437340995</v>
       </c>
       <c r="EB20" s="1">
         <f t="shared" si="31"/>
-        <v>2061.6692258777402</v>
+        <v>2181.3245622967584</v>
       </c>
       <c r="EC20" s="1">
         <f t="shared" si="31"/>
-        <v>2041.0525336189628</v>
+        <v>2159.5113166737906</v>
       </c>
       <c r="ED20" s="1">
         <f t="shared" si="31"/>
-        <v>2020.6420082827731</v>
+        <v>2137.9162035070526</v>
       </c>
       <c r="EE20" s="1">
         <f t="shared" si="31"/>
-        <v>2000.4355881999454</v>
+        <v>2116.5370414719819</v>
       </c>
       <c r="EF20" s="1">
         <f t="shared" si="31"/>
-        <v>1980.4312323179458</v>
+        <v>2095.3716710572621</v>
       </c>
       <c r="EG20" s="1">
         <f t="shared" si="31"/>
-        <v>1960.6269199947665</v>
+        <v>2074.4179543466894</v>
       </c>
       <c r="EH20" s="1">
         <f t="shared" si="31"/>
-        <v>1941.0206507948187</v>
+        <v>2053.6737748032224</v>
       </c>
       <c r="EI20" s="1">
         <f t="shared" si="31"/>
-        <v>1921.6104442868705</v>
+        <v>2033.1370370551901</v>
       </c>
       <c r="EJ20" s="1">
         <f t="shared" si="31"/>
-        <v>1902.3943398440017</v>
+        <v>2012.8056666846383</v>
       </c>
       <c r="EK20" s="1">
         <f t="shared" si="31"/>
-        <v>1883.3703964455617</v>
+        <v>1992.6776100177919</v>
       </c>
       <c r="EL20" s="1">
         <f t="shared" si="31"/>
-        <v>1864.536692481106</v>
+        <v>1972.750833917614</v>
       </c>
       <c r="EM20" s="1">
         <f t="shared" si="31"/>
-        <v>1845.891325556295</v>
+        <v>1953.0233255784378</v>
       </c>
       <c r="EN20" s="1">
         <f t="shared" si="31"/>
-        <v>1827.432412300732</v>
+        <v>1933.4930923226534</v>
       </c>
       <c r="EO20" s="1">
         <f t="shared" si="31"/>
-        <v>1809.1580881777247</v>
+        <v>1914.1581613994269</v>
       </c>
       <c r="EP20" s="1">
         <f t="shared" si="31"/>
-        <v>1791.0665072959475</v>
+        <v>1895.0165797854327</v>
       </c>
       <c r="EQ20" s="1">
         <f t="shared" si="31"/>
-        <v>1773.155842222988</v>
+        <v>1876.0664139875782</v>
       </c>
       <c r="ER20" s="1">
         <f t="shared" si="31"/>
-        <v>1755.4242838007581</v>
+        <v>1857.3057498477024</v>
       </c>
     </row>
     <row r="21" spans="2:148" x14ac:dyDescent="0.3">
@@ -3114,6 +3180,10 @@
         <f>554.4</f>
         <v>554.4</v>
       </c>
+      <c r="P21" s="5">
+        <f>552.7</f>
+        <v>552.70000000000005</v>
+      </c>
       <c r="T21" s="5">
         <f t="shared" ref="T21:Z21" si="32">554.4</f>
         <v>554.4</v>
@@ -3139,48 +3209,48 @@
         <v>554.4</v>
       </c>
       <c r="Z21" s="5">
-        <f t="shared" si="32"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" ref="AA21:AJ21" si="33">554.4</f>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
       <c r="AJ21" s="5">
-        <f t="shared" si="33"/>
-        <v>554.4</v>
+        <f>552.7</f>
+        <v>552.70000000000005</v>
       </c>
     </row>
     <row r="22" spans="2:148" x14ac:dyDescent="0.3">
@@ -3215,73 +3285,77 @@
         <f>O20/O21</f>
         <v>1.5349927849927851</v>
       </c>
+      <c r="P22" s="7">
+        <f>P20/P21</f>
+        <v>1.8563415958024243</v>
+      </c>
       <c r="T22" s="7">
-        <f t="shared" ref="T22:Z22" si="34">T20/T21</f>
+        <f t="shared" ref="T22:Z22" si="33">T20/T21</f>
         <v>1.6107503607503608</v>
       </c>
       <c r="U22" s="7">
+        <f t="shared" si="33"/>
+        <v>1.727994227994228</v>
+      </c>
+      <c r="V22" s="7">
+        <f t="shared" si="33"/>
+        <v>2.4062049062049065</v>
+      </c>
+      <c r="W22" s="7">
+        <f t="shared" si="33"/>
+        <v>4.5634920634920633</v>
+      </c>
+      <c r="X22" s="7">
+        <f t="shared" si="33"/>
+        <v>5.5339105339105341</v>
+      </c>
+      <c r="Y22" s="7">
+        <f t="shared" si="33"/>
+        <v>5.6475468975468974</v>
+      </c>
+      <c r="Z22" s="7">
+        <f t="shared" si="33"/>
+        <v>7.8081402569205691</v>
+      </c>
+      <c r="AA22" s="7">
+        <f t="shared" ref="AA22:AJ22" si="34">AA20/AA21</f>
+        <v>8.5271406072010123</v>
+      </c>
+      <c r="AB22" s="7">
         <f t="shared" si="34"/>
-        <v>1.727994227994228</v>
-      </c>
-      <c r="V22" s="7">
+        <v>8.9709340294409294</v>
+      </c>
+      <c r="AC22" s="7">
         <f t="shared" si="34"/>
-        <v>2.4062049062049065</v>
-      </c>
-      <c r="W22" s="7">
+        <v>9.3505993664292379</v>
+      </c>
+      <c r="AD22" s="7">
         <f t="shared" si="34"/>
-        <v>4.5634920634920633</v>
-      </c>
-      <c r="X22" s="7">
+        <v>9.7134118607137125</v>
+      </c>
+      <c r="AE22" s="7">
         <f t="shared" si="34"/>
-        <v>5.5339105339105341</v>
-      </c>
-      <c r="Y22" s="7">
+        <v>9.8688182890962732</v>
+      </c>
+      <c r="AF22" s="7">
         <f t="shared" si="34"/>
-        <v>5.6475468975468974</v>
-      </c>
-      <c r="Z22" s="7">
+        <v>9.9934777881495158</v>
+      </c>
+      <c r="AG22" s="7">
         <f t="shared" si="34"/>
-        <v>7.4576994227994247</v>
-      </c>
-      <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AJ22" si="35">AA20/AA21</f>
-        <v>7.9981860591630642</v>
-      </c>
-      <c r="AB22" s="7">
-        <f t="shared" si="35"/>
-        <v>8.4305625007647915</v>
-      </c>
-      <c r="AC22" s="7">
-        <f t="shared" si="35"/>
-        <v>8.7988063752245314</v>
-      </c>
-      <c r="AD22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.1500439388663217</v>
-      </c>
-      <c r="AE22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.2996380030978347</v>
-      </c>
-      <c r="AF22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.4185260614168627</v>
-      </c>
-      <c r="AG22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.5033769936502424</v>
+        <v>10.084049527032805</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.5884655930050915</v>
+        <f t="shared" si="34"/>
+        <v>10.174914262269716</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.6737692946396141</v>
+        <f t="shared" si="34"/>
+        <v>10.266049905595432</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="35"/>
-        <v>9.7592644274932709</v>
+        <f t="shared" si="34"/>
+        <v>10.357433264583694</v>
       </c>
     </row>
     <row r="24" spans="2:148" x14ac:dyDescent="0.3">
@@ -3293,11 +3367,11 @@
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
-        <f t="shared" ref="L24:M26" si="36">L3/H3-1</f>
+        <f t="shared" ref="L24:M26" si="35">L3/H3-1</f>
         <v>5.504587155963292E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>5.7135728542914155E-2</v>
       </c>
       <c r="N24" s="9"/>
@@ -3305,21 +3379,33 @@
         <f>O3/K3-1</f>
         <v>1.1249999999999982E-2</v>
       </c>
+      <c r="P24" s="9">
+        <f t="shared" ref="P24:P26" si="36">P3/L3-1</f>
+        <v>3.9613526570048352E-2</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" ref="Q24:Q26" si="37">Q3/M3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" ref="R24:R26" si="38">R3/N3-1</f>
+        <v>-1</v>
+      </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:X24" si="37">U3/T3-1</f>
+        <f t="shared" ref="U24:X24" si="39">U3/T3-1</f>
         <v>0.42482211594540997</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>8.9398280802292174E-2</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>8.6646126099045651E-2</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>8.0912863070539354E-2</v>
       </c>
       <c r="Y24" s="9">
@@ -3327,47 +3413,47 @@
         <v>6.4427383237364078E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AJ24" si="38">Z3/Y3-1</f>
+        <f t="shared" ref="Z24:AJ24" si="40">Z3/Y3-1</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="40"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="40"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="38"/>
+      <c r="AC24" s="9">
+        <f t="shared" si="40"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="38"/>
+      <c r="AD24" s="9">
+        <f t="shared" si="40"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="38"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="38"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AE24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3380,81 +3466,93 @@
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0.16225961538461542</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0.13063583815028901</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:O26" si="39">O4/K4-1</f>
+        <f t="shared" ref="O25:O26" si="41">O4/K4-1</f>
         <v>0.22876557191392988</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="36"/>
+        <v>0.25336091003102368</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="38"/>
+        <v>-1</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9">
-        <f t="shared" ref="U25:X25" si="40">U4/T4-1</f>
+        <f t="shared" ref="U25:X25" si="42">U4/T4-1</f>
         <v>0.63382899628252787</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.10693970420932875</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.12264474134977732</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>5.675923100396707E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" ref="Y25:AJ26" si="41">Y4/X4-1</f>
+        <f t="shared" ref="Y25:AJ26" si="43">Y4/X4-1</f>
         <v>0.10280103956107411</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.25</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" t="s">
@@ -3473,82 +3571,94 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>7.3801513877207681E-2</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>7.0182639031397542E-2</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>5.058365758754868E-2</v>
+      </c>
+      <c r="P26" s="10">
+        <f t="shared" si="36"/>
+        <v>8.0086156256119034E-2</v>
+      </c>
+      <c r="Q26" s="10">
+        <f t="shared" si="37"/>
+        <v>-1</v>
+      </c>
+      <c r="R26" s="10">
+        <f t="shared" si="38"/>
+        <v>-1</v>
       </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10">
-        <f t="shared" ref="U26:X26" si="42">U5/T5-1</f>
+        <f t="shared" ref="U26:X26" si="44">U5/T5-1</f>
         <v>0.45793658584470398</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>9.2512792889846596E-2</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>9.3122149636386098E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>7.6450358008682384E-2</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.1387419473105229E-2</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="41"/>
-        <v>6.2939479859210001E-2</v>
+        <f t="shared" si="43"/>
+        <v>7.9205612045365692E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="41"/>
-        <v>4.8541301327431841E-2</v>
+        <f t="shared" si="43"/>
+        <v>5.5948724034855735E-2</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="41"/>
-        <v>3.6855465734595638E-2</v>
+        <f t="shared" si="43"/>
+        <v>3.6484956744428532E-2</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="41"/>
-        <v>3.012537193073328E-2</v>
+        <f t="shared" si="43"/>
+        <v>2.9906340647923191E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="41"/>
-        <v>2.7814263102602599E-2</v>
+        <f t="shared" si="43"/>
+        <v>2.764685147014867E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.7982936754511458E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.7813184103244728E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.5437061811114816E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.5322333275749944E-2</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.2757518843885984E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.2699636900695532E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.2777238547657888E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.2719098080390845E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.2797044809846891E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.2738646923175168E-2</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="41"/>
-        <v>1.2816937234033432E-2</v>
+        <f t="shared" si="43"/>
+        <v>1.2758283067527243E-2</v>
       </c>
       <c r="AL26" t="s">
         <v>56</v>
@@ -3562,108 +3672,120 @@
         <v>49</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N28" si="43">(H3-H6)/H3</f>
+        <f t="shared" ref="H27:N28" si="45">(H3-H6)/H3</f>
         <v>0.65570846075433231</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.67290419161676651</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.66149999999999998</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.67560386473429956</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.68232239792305882</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.6901408450704225</v>
       </c>
       <c r="O27" s="9">
         <f>(O3-O6)/O3</f>
         <v>0.6566131025957973</v>
       </c>
+      <c r="P27" s="9">
+        <f t="shared" ref="P27:R27" si="46">(P3-P6)/P3</f>
+        <v>0.67193308550185871</v>
+      </c>
+      <c r="Q27" s="9" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" s="9" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:X27" si="44">(T3-T6)/T3</f>
+        <f t="shared" ref="T27:X27" si="47">(T3-T6)/T3</f>
         <v>0.53155254869940516</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.52181743757674992</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.54279702412264219</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.60089903181189486</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.65886116442738318</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27:Y28" si="45">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y27:Y28" si="48">(Y3-Y6)/Y3</f>
         <v>0.67764621025425253</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AJ27" si="46">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z27:AJ27" si="49">(Z3-Z6)/Z3</f>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="49"/>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" si="49"/>
         <v>0.68</v>
       </c>
-      <c r="AA27" s="9">
-        <f t="shared" si="46"/>
+      <c r="AC27" s="9">
+        <f t="shared" si="49"/>
+        <v>0.68</v>
+      </c>
+      <c r="AD27" s="9">
+        <f t="shared" si="49"/>
+        <v>0.68</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" si="49"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="46"/>
+      <c r="AF27" s="9">
+        <f t="shared" si="49"/>
         <v>0.68</v>
       </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="46"/>
+      <c r="AG27" s="9">
+        <f t="shared" si="49"/>
+        <v>0.68</v>
+      </c>
+      <c r="AH27" s="9">
+        <f t="shared" si="49"/>
+        <v>0.68</v>
+      </c>
+      <c r="AI27" s="9">
+        <f t="shared" si="49"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="46"/>
+      <c r="AJ27" s="9">
+        <f t="shared" si="49"/>
         <v>0.68</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.68</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.68</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.67999999999999994</v>
       </c>
       <c r="AL27" t="s">
         <v>57</v>
       </c>
       <c r="AM27" s="5">
         <f>NPV(AM26,Z20:ER20)</f>
-        <v>68637.351189598281</v>
+        <v>72599.222768261767</v>
       </c>
     </row>
     <row r="28" spans="2:148" x14ac:dyDescent="0.3">
@@ -3671,100 +3793,112 @@
         <v>50</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.30528846153846156</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.32601156069364162</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.26274065685164211</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.3391933815925543</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.32413087934560325</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.29465186680121092</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28" si="47">(O4-O7)/O4</f>
+        <f t="shared" ref="O28:P28" si="50">(O4-O7)/O4</f>
         <v>0.36958525345622117</v>
       </c>
+      <c r="P28" s="9">
+        <f t="shared" si="50"/>
+        <v>0.4273927392739274</v>
+      </c>
+      <c r="Q28" s="9" t="e">
+        <f t="shared" ref="Q28:R28" si="51">(Q4-Q7)/Q4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" s="9" t="e">
+        <f t="shared" si="51"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:X28" si="48">(T4-T7)/T4</f>
+        <f t="shared" ref="T28:X28" si="52">(T4-T7)/T4</f>
         <v>0.19888475836431227</v>
       </c>
       <c r="U28" s="9">
+        <f t="shared" si="52"/>
+        <v>0.25255972696245732</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="52"/>
+        <v>0.29976019184652281</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="52"/>
+        <v>0.32224595666768385</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="52"/>
+        <v>0.32486283569159691</v>
+      </c>
+      <c r="Y28" s="9">
         <f t="shared" si="48"/>
-        <v>0.25255972696245732</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.29976019184652281</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.32224595666768385</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.32486283569159691</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="45"/>
         <v>0.30610107357947108</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AJ28" si="49">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z28:AJ28" si="53">(Z4-Z7)/Z4</f>
         <v>0.35</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="AL28" t="s">
@@ -3772,7 +3906,7 @@
       </c>
       <c r="AM28" s="5">
         <f>Main!D8</f>
-        <v>-27120</v>
+        <v>-28588</v>
       </c>
     </row>
     <row r="29" spans="2:148" x14ac:dyDescent="0.3">
@@ -3780,108 +3914,120 @@
         <v>51</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="50">H9/H5</f>
+        <f t="shared" ref="H29:N29" si="54">H9/H5</f>
         <v>0.59440706476030281</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.6113277241945414</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.58939176735613352</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.61190522811826908</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.61514860977948227</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.61550180917920394</v>
       </c>
       <c r="O29" s="9">
         <f>O9/O5</f>
         <v>0.59590643274853805</v>
       </c>
+      <c r="P29" s="9">
+        <f t="shared" ref="P29:R29" si="55">P9/P5</f>
+        <v>0.6182015953589558</v>
+      </c>
+      <c r="Q29" s="9" t="e">
+        <f t="shared" si="55"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R29" s="9" t="e">
+        <f t="shared" si="55"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29:X29" si="51">T9/T5</f>
+        <f t="shared" ref="T29:X29" si="56">T9/T5</f>
         <v>0.47884558751349759</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>0.47401023431187717</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>0.4990755577468261</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>0.54941647403732308</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>0.59828209291363332</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="52">Y9/Y5</f>
+        <f t="shared" ref="Y29" si="57">Y9/Y5</f>
         <v>0.60828118889323424</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AJ29" si="53">Z9/Z5</f>
-        <v>0.60754900432267311</v>
+        <f t="shared" ref="Z29:AJ29" si="58">Z9/Z5</f>
+        <v>0.60864100890414707</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.60053851867976382</v>
+        <f t="shared" si="58"/>
+        <v>0.60228520391912321</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.59646568157144875</v>
+        <f t="shared" si="58"/>
+        <v>0.59827268965463354</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.59404310587137132</v>
+        <f t="shared" si="58"/>
+        <v>0.59588463382836521</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.59218769570037544</v>
+        <f t="shared" si="58"/>
+        <v>0.59405497486430814</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.59028848011660462</v>
+        <f t="shared" si="58"/>
+        <v>0.59218150095012645</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.58900187815176919</v>
+        <f t="shared" si="58"/>
+        <v>0.5909119822770571</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.58835112792729316</v>
+        <f t="shared" si="58"/>
+        <v>0.59026976334710357</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.58769752127504782</v>
+        <f t="shared" si="58"/>
+        <v>0.58962465153521859</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.58704107127689376</v>
+        <f t="shared" si="58"/>
+        <v>0.58897665877159933</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.58638179140594426</v>
+        <f t="shared" si="58"/>
+        <v>0.58832579737412216</v>
       </c>
       <c r="AL29" t="s">
         <v>59</v>
       </c>
       <c r="AM29" s="5">
         <f>AM27+AM28</f>
-        <v>41517.351189598281</v>
+        <v>44011.222768261767</v>
       </c>
     </row>
     <row r="30" spans="2:148" x14ac:dyDescent="0.3">
@@ -3893,11 +4039,11 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:M30" si="54">L10/H10-1</f>
+        <f t="shared" ref="L30:M30" si="59">L10/H10-1</f>
         <v>5.8962264150941301E-4</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-2.7845036319612548E-2</v>
       </c>
       <c r="N30" s="9"/>
@@ -3905,21 +4051,33 @@
         <f>O10/K10-1</f>
         <v>-8.8391278727165679E-3</v>
       </c>
+      <c r="P30" s="9">
+        <f t="shared" ref="P30" si="60">P10/L10-1</f>
+        <v>8.2498526812020412E-3</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" ref="Q30" si="61">Q10/M10-1</f>
+        <v>-1</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" ref="R30" si="62">R10/N10-1</f>
+        <v>-1</v>
+      </c>
       <c r="T30" s="9"/>
       <c r="U30" s="9">
-        <f t="shared" ref="U30:X30" si="55">U10/T10-1</f>
+        <f t="shared" ref="U30:X30" si="63">U10/T10-1</f>
         <v>0.72107186358099873</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>2.7954706298655374E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4.2857142857142927E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>8.5327611817131555E-2</v>
       </c>
       <c r="Y30" s="9">
@@ -3927,47 +4085,47 @@
         <v>-1.8248175182481452E-3</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AJ30" si="56">Z10/Y10-1</f>
+        <f t="shared" ref="Z30:AJ30" si="64">Z10/Y10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL30" t="s">
@@ -3975,7 +4133,7 @@
       </c>
       <c r="AM30" s="4">
         <f>AM29/AJ21</f>
-        <v>74.886997095235003</v>
+        <v>79.629496595371378</v>
       </c>
     </row>
     <row r="31" spans="2:148" x14ac:dyDescent="0.3">
@@ -3983,108 +4141,120 @@
         <v>53</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="57">H13/H5</f>
+        <f t="shared" ref="H31:N31" si="65">H13/H5</f>
         <v>0.23780487804878048</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>0.30843422942745741</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>0.24185951259471636</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>0.27961621304092421</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>0.30719079578139979</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>0.3176537802323367</v>
       </c>
       <c r="O31" s="9">
         <f>O13/O5</f>
         <v>0.27192982456140352</v>
       </c>
+      <c r="P31" s="9">
+        <f t="shared" ref="P31:R31" si="66">P13/P5</f>
+        <v>0.30746918056562728</v>
+      </c>
+      <c r="Q31" s="9" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" s="9" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:X31" si="58">T13/T5</f>
+        <f t="shared" ref="T31:X31" si="67">T13/T5</f>
         <v>0.15794640227741238</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="67"/>
         <v>0.12469701050363588</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="67"/>
         <v>0.14100825835079503</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="67"/>
         <v>0.21085865704459605</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="67"/>
         <v>0.26260933326349972</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="59">Y13/Y5</f>
+        <f t="shared" ref="Y31" si="68">Y13/Y5</f>
         <v>0.28739734063355493</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31:AJ31" si="60">Z13/Z5</f>
-        <v>0.30264670942889116</v>
+        <f t="shared" ref="Z31:AJ31" si="69">Z13/Z5</f>
+        <v>0.30833429892694536</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.30684353742069492</v>
+        <f t="shared" si="69"/>
+        <v>0.31504608882458968</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31037765785495075</v>
+        <f t="shared" si="69"/>
+        <v>0.31837330051471646</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31354433181235103</v>
+        <f t="shared" si="69"/>
+        <v>0.32139522457444397</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31655057723461483</v>
+        <f t="shared" si="69"/>
+        <v>0.32427912438624762</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31681288480065545</v>
+        <f t="shared" si="69"/>
+        <v>0.32447656920186363</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31699058207354169</v>
+        <f t="shared" si="69"/>
+        <v>0.32461036336810634</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31708045955187619</v>
+        <f t="shared" si="69"/>
+        <v>0.3246780466153884</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31717073154183012</v>
+        <f t="shared" si="69"/>
+        <v>0.32474603474257036</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31726139623662009</v>
+        <f t="shared" si="69"/>
+        <v>0.32481432649233249</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31735245177542581</v>
+        <f t="shared" si="69"/>
+        <v>0.32488292056649809</v>
       </c>
       <c r="AL31" t="s">
         <v>61</v>
       </c>
       <c r="AM31" s="4">
         <f>Main!D3</f>
-        <v>161.83000000000001</v>
+        <v>140.47999999999999</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -4092,100 +4262,112 @@
         <v>27</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:N32" si="61">H18/H17</f>
+        <f t="shared" ref="H32:N32" si="70">H18/H17</f>
         <v>0.20733104238258879</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
         <v>0.1975206611570248</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
         <v>0.16757940854326397</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
         <v>0.19420035149384884</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
         <v>5.8221872541306056E-2</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="70"/>
         <v>0.16300675675675674</v>
       </c>
       <c r="O32" s="9">
         <f>O18/O17</f>
         <v>0.18164435946462715</v>
       </c>
+      <c r="P32" s="9">
+        <f t="shared" ref="P32:R32" si="71">P18/P17</f>
+        <v>0.19040247678018576</v>
+      </c>
+      <c r="Q32" s="9" t="e">
+        <f t="shared" si="71"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" s="9" t="e">
+        <f t="shared" si="71"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T32" s="9">
-        <f t="shared" ref="T32:X32" si="62">T18/T17</f>
+        <f t="shared" ref="T32:X32" si="72">T18/T17</f>
         <v>0.18282548476454294</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>0.16737830913748933</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>0.21788715486194477</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>0.1891520768966701</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>0.19343252950230888</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32" si="63">Y18/Y17</f>
+        <f t="shared" ref="Y32" si="73">Y18/Y17</f>
         <v>0.14225477141588994</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" ref="Z32:AJ32" si="64">Z18/Z17</f>
+        <f t="shared" ref="Z32:AJ32" si="74">Z18/Z17</f>
         <v>0.18</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="AC32" s="9">
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="64"/>
+      <c r="AD32" s="9">
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="64"/>
+      <c r="AE32" s="9">
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="64"/>
+      <c r="AF32" s="9">
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="64"/>
+      <c r="AG32" s="9">
+        <f t="shared" si="74"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="AH32" s="9">
+        <f t="shared" si="74"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="AI32" s="9">
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="64"/>
-        <v>0.17999999999999997</v>
-      </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="64"/>
-        <v>0.18</v>
-      </c>
-      <c r="AI32" s="9">
-        <f t="shared" si="64"/>
-        <v>0.18</v>
-      </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>0.18</v>
       </c>
       <c r="AL32" s="1" t="s">
@@ -4193,7 +4375,7 @@
       </c>
       <c r="AM32" s="10">
         <f>AM30/AM31-1</f>
-        <v>-0.53724898291271705</v>
+        <v>-0.43316132833590981</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
@@ -4201,107 +4383,119 @@
         <v>54</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:N33" si="65">H20/H5</f>
+        <f t="shared" ref="H33:N33" si="75">H20/H5</f>
         <v>0.14360807401177461</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.19536219987687256</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.15052221994675405</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.1750538476600744</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.10814956855225312</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.17863264140163779</v>
       </c>
       <c r="O33" s="9">
         <f>O20/O5</f>
         <v>0.16588693957115011</v>
       </c>
+      <c r="P33" s="9">
+        <f t="shared" ref="P33:R33" si="76">P20/P5</f>
+        <v>0.18600435097897028</v>
+      </c>
+      <c r="Q33" s="9" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" s="9" t="e">
+        <f t="shared" si="76"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T33" s="9">
-        <f t="shared" ref="T33:X33" si="66">T20/T5</f>
+        <f t="shared" ref="T33:X33" si="77">T20/T5</f>
         <v>8.766074408559929E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>6.4503097225962827E-2</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>8.2213731048933814E-2</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0.14263967976546202</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0.1606871628345467</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33" si="67">Y20/Y5</f>
+        <f t="shared" ref="Y33" si="78">Y20/Y5</f>
         <v>0.15306022682831444</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" ref="Z33:AJ33" si="68">Z20/Z5</f>
-        <v>0.19015110085823392</v>
+        <f t="shared" ref="Z33:AJ33" si="79">Z20/Z5</f>
+        <v>0.1954844246504045</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.194491188248854</v>
+        <f t="shared" si="79"/>
+        <v>0.2021739280162074</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.19771825003227017</v>
+        <f t="shared" si="79"/>
+        <v>0.20520899076042073</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.20031980205263447</v>
+        <f t="shared" si="79"/>
+        <v>0.20768275646369294</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.20267895713042686</v>
+        <f t="shared" si="79"/>
+        <v>0.20993695675411811</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.20235364255310326</v>
+        <f t="shared" si="79"/>
+        <v>0.20956279109037529</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.2018249791771444</v>
+        <f t="shared" si="79"/>
+        <v>0.20900743421653811</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.20107795245306365</v>
+        <f t="shared" si="79"/>
+        <v>0.20825689935963879</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.20031878539407083</v>
+        <f t="shared" si="79"/>
+        <v>0.20749430741328945</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.19954730395409886</v>
+        <f t="shared" si="79"/>
+        <v>0.20671948569222967</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="68"/>
-        <v>0.19876333204230015</v>
+        <f t="shared" si="79"/>
+        <v>0.20593225946595745</v>
       </c>
       <c r="AL33" t="s">
         <v>63</v>
       </c>
       <c r="AM33" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/FI.xlsx
+++ b/Financial Analysis/FI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C11E6F3-3A14-4312-A06A-32A696AA40CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAC6815-1F12-4A07-9891-7528B2DD210B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9F0C41CC-C0DB-440C-AB99-1B4D33A170AF}"/>
   </bookViews>
@@ -746,14 +746,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>140.47999999999999</v>
+        <v>125.45</v>
       </c>
       <c r="E3" s="3">
-        <v>45861</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45861</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45958</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>77643.296000000002</v>
+        <v>69336.215000000011</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>106231.296</v>
+        <v>97924.215000000011</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
         <v>17821.554400000001</v>
       </c>
       <c r="AB3" s="5">
-        <f t="shared" ref="AA3:AD3" si="0">AA3*1.02</f>
+        <f t="shared" ref="AB3:AD3" si="0">AA3*1.02</f>
         <v>18177.985488000002</v>
       </c>
       <c r="AC3" s="5">
@@ -1135,95 +1135,95 @@
         <v>4873</v>
       </c>
       <c r="K5" s="8">
-        <f>K3+K4</f>
+        <f t="shared" ref="K5:P5" si="3">K3+K4</f>
         <v>4883</v>
       </c>
       <c r="L5" s="8">
-        <f>L3+L4</f>
+        <f t="shared" si="3"/>
         <v>5107</v>
       </c>
       <c r="M5" s="8">
-        <f>M3+M4</f>
+        <f t="shared" si="3"/>
         <v>5215</v>
       </c>
       <c r="N5" s="8">
-        <f>N3+N4</f>
+        <f t="shared" si="3"/>
         <v>5251</v>
       </c>
       <c r="O5" s="8">
-        <f>O3+O4</f>
+        <f t="shared" si="3"/>
         <v>5130</v>
       </c>
       <c r="P5" s="8">
-        <f>P3+P4</f>
+        <f t="shared" si="3"/>
         <v>5516</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:Y5" si="3">T3+T4</f>
+        <f t="shared" ref="T5:Y5" si="4">T3+T4</f>
         <v>10187</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14852</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16226</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17737</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19093</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20456</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5:AJ5" si="4">Z3+Z4</f>
+        <f t="shared" ref="Z5:AJ5" si="5">Z3+Z4</f>
         <v>22076.23</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>23311.366900000001</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24161.881113000003</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24884.474560260001</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25572.451932340202</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26027.978726582354</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26426.788091125178</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26762.398704334089</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27102.792278321038</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27448.045179786728</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27798.235109840723</v>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         <v>1346</v>
       </c>
       <c r="N6" s="5">
-        <f t="shared" ref="N6:N7" si="5">Y6-M6-L6-K6</f>
+        <f t="shared" ref="N6:N7" si="6">Y6-M6-L6-K6</f>
         <v>1320</v>
       </c>
       <c r="O6" s="5">
@@ -1279,43 +1279,43 @@
         <v>5536.7936</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AJ6" si="6">AA3*0.32</f>
+        <f t="shared" ref="AA6:AJ6" si="7">AA3*0.32</f>
         <v>5702.8974080000007</v>
       </c>
       <c r="AB6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5816.9553561600005</v>
       </c>
       <c r="AC6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5933.2944632832005</v>
       </c>
       <c r="AD6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6051.9603525488646</v>
       </c>
       <c r="AE6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6112.479956074354</v>
       </c>
       <c r="AF6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6173.6047556350977</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6235.3408031914487</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6297.6942112233628</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6360.6711533355974</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6424.2778648689527</v>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         <v>661</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>699</v>
       </c>
       <c r="O7" s="5">
@@ -1371,43 +1371,43 @@
         <v>3102.9375</v>
       </c>
       <c r="AA7" s="5">
-        <f t="shared" ref="AA7:AJ7" si="7">AA4*0.65</f>
+        <f t="shared" ref="AA7:AJ7" si="8">AA4*0.65</f>
         <v>3568.3781250000002</v>
       </c>
       <c r="AB7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3889.5321562500003</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4122.9040856250003</v>
       </c>
       <c r="AD7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4329.0492899062501</v>
       </c>
       <c r="AE7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4502.2112615025007</v>
       </c>
       <c r="AF7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4637.2775993475752</v>
       </c>
       <c r="AG7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4730.023151334527</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4824.6236143612177</v>
       </c>
       <c r="AI7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4921.1160866484424</v>
       </c>
       <c r="AJ7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5019.5384083814106</v>
       </c>
     </row>
@@ -1424,95 +1424,95 @@
         <v>1894</v>
       </c>
       <c r="K8" s="5">
-        <f>K6+K7</f>
+        <f t="shared" ref="K8:P8" si="9">K6+K7</f>
         <v>2005</v>
       </c>
       <c r="L8" s="5">
-        <f>L6+L7</f>
+        <f t="shared" si="9"/>
         <v>1982</v>
       </c>
       <c r="M8" s="5">
-        <f>M6+M7</f>
+        <f t="shared" si="9"/>
         <v>2007</v>
       </c>
       <c r="N8" s="5">
-        <f>N6+N7</f>
+        <f t="shared" si="9"/>
         <v>2019</v>
       </c>
       <c r="O8" s="5">
-        <f>O6+O7</f>
+        <f t="shared" si="9"/>
         <v>2073</v>
       </c>
       <c r="P8" s="5">
-        <f>P6+P7</f>
+        <f t="shared" si="9"/>
         <v>2106</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" ref="T8:Z8" si="8">T6+T7</f>
+        <f t="shared" ref="T8:Z8" si="10">T6+T7</f>
         <v>5309</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7812</v>
       </c>
       <c r="V8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8128</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7992</v>
       </c>
       <c r="X8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7670</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8013</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8639.7311000000009</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AJ8" si="9">AA6+AA7</f>
+        <f t="shared" ref="AA8:AJ8" si="11">AA6+AA7</f>
         <v>9271.275533</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9706.4875124099999</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10056.1985489082</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10381.009642455116</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10614.691217576856</v>
       </c>
       <c r="AF8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10810.882354982674</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10965.363954525976</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11122.317825584581</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11281.78723998404</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11443.816273250362</v>
       </c>
     </row>
@@ -1529,95 +1529,95 @@
         <v>2979</v>
       </c>
       <c r="K9" s="8">
-        <f>K5-K8</f>
+        <f t="shared" ref="K9:P9" si="12">K5-K8</f>
         <v>2878</v>
       </c>
       <c r="L9" s="8">
-        <f>L5-L8</f>
+        <f t="shared" si="12"/>
         <v>3125</v>
       </c>
       <c r="M9" s="8">
-        <f>M5-M8</f>
+        <f t="shared" si="12"/>
         <v>3208</v>
       </c>
       <c r="N9" s="8">
-        <f>N5-N8</f>
+        <f t="shared" si="12"/>
         <v>3232</v>
       </c>
       <c r="O9" s="8">
-        <f>O5-O8</f>
+        <f t="shared" si="12"/>
         <v>3057</v>
       </c>
       <c r="P9" s="8">
-        <f>P5-P8</f>
+        <f t="shared" si="12"/>
         <v>3410</v>
       </c>
       <c r="T9" s="8">
-        <f t="shared" ref="T9:Z9" si="10">T5-T8</f>
+        <f t="shared" ref="T9:Z9" si="13">T5-T8</f>
         <v>4878</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7040</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>8098</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>9745</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>11423</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>12443</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>13436.498899999999</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AJ9" si="11">AA5-AA8</f>
+        <f t="shared" ref="AA9:AJ9" si="14">AA5-AA8</f>
         <v>14040.091367000001</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>14455.393600590003</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>14828.276011351802</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>15191.442289885086</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>15413.287509005499</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>15615.905736142504</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>15797.034749808114</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>15980.474452736456</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>16166.257939802688</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>16354.418836590361</v>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
         <v>1606</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" ref="N10:N11" si="12">Y10-M10-L10-K10</f>
+        <f t="shared" ref="N10:N11" si="15">Y10-M10-L10-K10</f>
         <v>1564</v>
       </c>
       <c r="O10" s="5">
@@ -1673,43 +1673,43 @@
         <v>6629.64</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" ref="AA10:AJ10" si="13">Z10*1.01</f>
+        <f t="shared" ref="AA10:AJ10" si="16">Z10*1.01</f>
         <v>6695.9364000000005</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6762.8957640000008</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6830.5247216400012</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6898.8299688564011</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6967.8182685449656</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7037.496451230415</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7107.8714157427194</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7178.9501299001467</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7250.7396311991479</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7323.2470275111391</v>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O11" s="5">
@@ -1807,95 +1807,95 @@
         <v>1476</v>
       </c>
       <c r="K12" s="5">
-        <f>SUM(K10:K11)</f>
+        <f t="shared" ref="K12:P12" si="17">SUM(K10:K11)</f>
         <v>1697</v>
       </c>
       <c r="L12" s="5">
-        <f>SUM(L10:L11)</f>
+        <f t="shared" si="17"/>
         <v>1697</v>
       </c>
       <c r="M12" s="5">
-        <f>SUM(M10:M11)</f>
+        <f t="shared" si="17"/>
         <v>1606</v>
       </c>
       <c r="N12" s="5">
-        <f>SUM(N10:N11)</f>
+        <f t="shared" si="17"/>
         <v>1564</v>
       </c>
       <c r="O12" s="5">
-        <f>SUM(O10:O11)</f>
+        <f t="shared" si="17"/>
         <v>1662</v>
       </c>
       <c r="P12" s="5">
-        <f>SUM(P10:P11)</f>
+        <f t="shared" si="17"/>
         <v>1714</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:Z12" si="14">SUM(T10:T11)</f>
+        <f t="shared" ref="T12:Z12" si="18">SUM(T10:T11)</f>
         <v>3269</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5188</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5810</v>
       </c>
       <c r="W12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6005</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6409</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6564</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6629.64</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" ref="AA12:AJ12" si="15">SUM(AA10:AA11)</f>
+        <f t="shared" ref="AA12:AJ12" si="19">SUM(AA10:AA11)</f>
         <v>6695.9364000000005</v>
       </c>
       <c r="AB12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6762.8957640000008</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6830.5247216400012</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6898.8299688564011</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6967.8182685449656</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7037.496451230415</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7107.8714157427194</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7178.9501299001467</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7250.7396311991479</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7323.2470275111391</v>
       </c>
     </row>
@@ -1912,95 +1912,95 @@
         <v>1503</v>
       </c>
       <c r="K13" s="8">
-        <f>K9-K12</f>
+        <f t="shared" ref="K13:P13" si="20">K9-K12</f>
         <v>1181</v>
       </c>
       <c r="L13" s="8">
-        <f>L9-L12</f>
+        <f t="shared" si="20"/>
         <v>1428</v>
       </c>
       <c r="M13" s="8">
-        <f>M9-M12</f>
+        <f t="shared" si="20"/>
         <v>1602</v>
       </c>
       <c r="N13" s="8">
-        <f>N9-N12</f>
+        <f t="shared" si="20"/>
         <v>1668</v>
       </c>
       <c r="O13" s="8">
-        <f>O9-O12</f>
+        <f t="shared" si="20"/>
         <v>1395</v>
       </c>
       <c r="P13" s="8">
-        <f>P9-P12</f>
+        <f t="shared" si="20"/>
         <v>1696</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13:Z13" si="16">T9-T12</f>
+        <f t="shared" ref="T13:Z13" si="21">T9-T12</f>
         <v>1609</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>1852</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2288</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>3740</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>5014</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>5879</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>6806.8588999999984</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AJ13" si="17">AA9-AA12</f>
+        <f t="shared" ref="AA13:AJ13" si="22">AA9-AA12</f>
         <v>7344.1549670000004</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>7692.4978365900024</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>7997.7512897118004</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8292.612321028686</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8445.4692404605339</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8578.4092849120898</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8689.1633340653934</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8801.5243228363106</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>8915.5183086035395</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>9031.1718090792219</v>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
         <v>326</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" ref="N14:N15" si="18">Y14-M14-L14-K14</f>
+        <f t="shared" ref="N14:N15" si="23">Y14-M14-L14-K14</f>
         <v>323</v>
       </c>
       <c r="O14" s="5">
@@ -2057,43 +2057,43 @@
         <v>1230.8500000000001</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" ref="AA14:AJ14" si="19">Z14*1.03</f>
+        <f t="shared" ref="AA14:AJ14" si="24">Z14*1.03</f>
         <v>1267.7755000000002</v>
       </c>
       <c r="AB14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1305.8087650000002</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1344.9830279500002</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1385.3325187885002</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1426.8924943521554</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1469.6992691827202</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1513.7902472582018</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1559.2039546759479</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1605.9800733162265</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1654.1594755157132</v>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>161</v>
       </c>
       <c r="O15" s="5">
@@ -2149,43 +2149,43 @@
         <v>181.56</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" ref="AA15:AJ15" si="20">Z15*1.02</f>
+        <f t="shared" ref="AA15:AJ15" si="25">Z15*1.02</f>
         <v>185.19120000000001</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>188.89502400000001</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>192.67292448000001</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>196.52638296960001</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>200.45691062899201</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>204.46604884157185</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>208.55536981840328</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>212.72647721477134</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.98100675906676</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>221.32062689424811</v>
       </c>
     </row>
@@ -2202,95 +2202,95 @@
         <v>293</v>
       </c>
       <c r="K16" s="5">
-        <f>SUM(K14:K15)</f>
+        <f t="shared" ref="K16:P16" si="26">SUM(K14:K15)</f>
         <v>268</v>
       </c>
       <c r="L16" s="5">
-        <f>SUM(L14:L15)</f>
+        <f t="shared" si="26"/>
         <v>290</v>
       </c>
       <c r="M16" s="5">
-        <f>SUM(M14:M15)</f>
+        <f t="shared" si="26"/>
         <v>331</v>
       </c>
       <c r="N16" s="5">
-        <f>SUM(N14:N15)</f>
+        <f t="shared" si="26"/>
         <v>484</v>
       </c>
       <c r="O16" s="5">
-        <f>SUM(O14:O15)</f>
+        <f t="shared" si="26"/>
         <v>349</v>
       </c>
       <c r="P16" s="5">
-        <f>SUM(P14:P15)</f>
+        <f t="shared" si="26"/>
         <v>404</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" ref="T16:Z16" si="21">SUM(T14:T15)</f>
+        <f t="shared" ref="T16:Z16" si="27">SUM(T14:T15)</f>
         <v>526</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>681</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>622</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>827</v>
       </c>
       <c r="X16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>1116</v>
       </c>
       <c r="Y16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>1373</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>1412.41</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AJ16" si="22">SUM(AA14:AA15)</f>
+        <f t="shared" ref="AA16:AJ16" si="28">SUM(AA14:AA15)</f>
         <v>1452.9667000000002</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1494.7037890000001</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1537.6559524300001</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1581.8589017581003</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1627.3494049811475</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1674.165318024292</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1722.3456170766051</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1771.9304318907193</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1822.9610800752932</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1875.4801024099613</v>
       </c>
     </row>
@@ -2307,95 +2307,95 @@
         <v>1210</v>
       </c>
       <c r="K17" s="8">
-        <f>K13-K16</f>
+        <f t="shared" ref="K17:P17" si="29">K13-K16</f>
         <v>913</v>
       </c>
       <c r="L17" s="8">
-        <f>L13-L16</f>
+        <f t="shared" si="29"/>
         <v>1138</v>
       </c>
       <c r="M17" s="8">
-        <f>M13-M16</f>
+        <f t="shared" si="29"/>
         <v>1271</v>
       </c>
       <c r="N17" s="8">
-        <f>N13-N16</f>
+        <f t="shared" si="29"/>
         <v>1184</v>
       </c>
       <c r="O17" s="8">
-        <f>O13-O16</f>
+        <f t="shared" si="29"/>
         <v>1046</v>
       </c>
       <c r="P17" s="8">
-        <f>P13-P16</f>
+        <f t="shared" si="29"/>
         <v>1292</v>
       </c>
       <c r="T17" s="8">
-        <f t="shared" ref="T17:Z17" si="23">T13-T16</f>
+        <f t="shared" ref="T17:Z17" si="30">T13-T16</f>
         <v>1083</v>
       </c>
       <c r="U17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>1171</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>1666</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>2913</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>3898</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>4506</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>5394.4488999999985</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" ref="AA17:AJ17" si="24">AA13-AA16</f>
+        <f t="shared" ref="AA17:AJ17" si="31">AA13-AA16</f>
         <v>5891.1882670000005</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6197.7940475900023</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6460.0953372818003</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6710.7534192705862</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6818.1198354793869</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6904.2439668877978</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6966.8177169887886</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>7029.5938909455908</v>
       </c>
       <c r="AI17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>7092.557228528246</v>
       </c>
       <c r="AJ17" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>7155.6917066692604</v>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
         <v>74</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" ref="N18:N19" si="25">Y18-M18-L18-K18</f>
+        <f t="shared" ref="N18:N19" si="32">Y18-M18-L18-K18</f>
         <v>193</v>
       </c>
       <c r="O18" s="5">
@@ -2451,43 +2451,43 @@
         <v>971.00080199999968</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" ref="AA18:AJ18" si="26">AA17*0.18</f>
+        <f t="shared" ref="AA18:AJ18" si="33">AA17*0.18</f>
         <v>1060.4138880600001</v>
       </c>
       <c r="AB18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1115.6029285662003</v>
       </c>
       <c r="AC18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1162.817160710724</v>
       </c>
       <c r="AD18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1207.9356154687055</v>
       </c>
       <c r="AE18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1227.2615703862896</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1242.7639140398035</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1254.0271890579818</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1265.3269003702062</v>
       </c>
       <c r="AI18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1276.6603011350842</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>1288.0245072004668</v>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         <v>633</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>53</v>
       </c>
       <c r="O19" s="5">
@@ -2555,43 +2555,43 @@
         <v>107.88897799999997</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AJ19" si="27">AA17*0.02</f>
+        <f t="shared" ref="AA19:AJ19" si="34">AA17*0.02</f>
         <v>117.82376534000001</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>123.95588095180005</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>129.20190674563599</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>134.21506838541171</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>136.36239670958773</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>138.08487933775595</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>139.33635433977577</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>140.59187781891183</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>141.85114457056491</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>143.11383413338521</v>
       </c>
     </row>
@@ -2608,95 +2608,95 @@
         <v>952</v>
       </c>
       <c r="K20" s="8">
-        <f>K17-K18-K19</f>
+        <f t="shared" ref="K20:P20" si="35">K17-K18-K19</f>
         <v>735</v>
       </c>
       <c r="L20" s="8">
-        <f>L17-L18-L19</f>
+        <f t="shared" si="35"/>
         <v>894</v>
       </c>
       <c r="M20" s="8">
-        <f>M17-M18-M19</f>
+        <f t="shared" si="35"/>
         <v>564</v>
       </c>
       <c r="N20" s="8">
-        <f>N17-N18-N19</f>
+        <f t="shared" si="35"/>
         <v>938</v>
       </c>
       <c r="O20" s="8">
-        <f>O17-O18-O19</f>
+        <f t="shared" si="35"/>
         <v>851</v>
       </c>
       <c r="P20" s="8">
-        <f>P17-P18-P19</f>
+        <f t="shared" si="35"/>
         <v>1026</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" ref="T20:Z20" si="28">T17-T18-T19</f>
+        <f t="shared" ref="T20:Z20" si="36">T17-T18-T19</f>
         <v>893</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>958</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1334</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>2530</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>3068</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>3131</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>4315.559119999999</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" ref="AA20:AJ20" si="29">AA17-AA18-AA19</f>
+        <f t="shared" ref="AA20:AJ20" si="37">AA17-AA18-AA19</f>
         <v>4712.9506136</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>4958.2352380720022</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5168.0762698254402</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5368.6027354164689</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5454.4958683835102</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5523.3951735102382</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5573.4541735910316</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5623.675112756473</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5674.0457828225963</v>
       </c>
       <c r="AJ20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>5724.5533653354078</v>
       </c>
       <c r="AK20" s="1">
@@ -2704,447 +2704,447 @@
         <v>5667.3078316820538</v>
       </c>
       <c r="AL20" s="1">
-        <f t="shared" ref="AL20:CW20" si="30">AK20*(1+$AM$25)</f>
+        <f t="shared" ref="AL20:CW20" si="38">AK20*(1+$AM$25)</f>
         <v>5610.6347533652333</v>
       </c>
       <c r="AM20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5554.528405831581</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5498.9831217732653</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5443.9932905555324</v>
       </c>
       <c r="AP20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5389.5533576499774</v>
       </c>
       <c r="AQ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5335.657824073478</v>
       </c>
       <c r="AR20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5282.301245832743</v>
       </c>
       <c r="AS20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5229.4782333744151</v>
       </c>
       <c r="AT20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5177.1834510406707</v>
       </c>
       <c r="AU20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5125.4116165302639</v>
       </c>
       <c r="AV20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5074.1575003649614</v>
       </c>
       <c r="AW20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>5023.4159253613116</v>
       </c>
       <c r="AX20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4973.1817661076984</v>
       </c>
       <c r="AY20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4923.4499484466214</v>
       </c>
       <c r="AZ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4874.2154489621553</v>
       </c>
       <c r="BA20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4825.4732944725338</v>
       </c>
       <c r="BB20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4777.2185615278086</v>
       </c>
       <c r="BC20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4729.4463759125301</v>
       </c>
       <c r="BD20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4682.1519121534047</v>
       </c>
       <c r="BE20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4635.3303930318707</v>
       </c>
       <c r="BF20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4588.9770891015523</v>
       </c>
       <c r="BG20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4543.087318210537</v>
       </c>
       <c r="BH20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4497.6564450284313</v>
       </c>
       <c r="BI20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4452.6798805781473</v>
       </c>
       <c r="BJ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4408.153081772366</v>
       </c>
       <c r="BK20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4364.0715509546426</v>
       </c>
       <c r="BL20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4320.4308354450959</v>
       </c>
       <c r="BM20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4277.2265270906446</v>
       </c>
       <c r="BN20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4234.4542618197383</v>
       </c>
       <c r="BO20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4192.1097192015413</v>
       </c>
       <c r="BP20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4150.1886220095257</v>
       </c>
       <c r="BQ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4108.6867357894307</v>
       </c>
       <c r="BR20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4067.5998684315364</v>
       </c>
       <c r="BS20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>4026.923869747221</v>
       </c>
       <c r="BT20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3986.6546310497488</v>
       </c>
       <c r="BU20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3946.7880847392512</v>
       </c>
       <c r="BV20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3907.3202038918585</v>
       </c>
       <c r="BW20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3868.2470018529398</v>
       </c>
       <c r="BX20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3829.5645318344104</v>
       </c>
       <c r="BY20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3791.2688865160662</v>
       </c>
       <c r="BZ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3753.3561976509054</v>
       </c>
       <c r="CA20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3715.8226356743962</v>
       </c>
       <c r="CB20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3678.6644093176524</v>
       </c>
       <c r="CC20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3641.8777652244758</v>
       </c>
       <c r="CD20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3605.4589875722309</v>
       </c>
       <c r="CE20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3569.4043976965086</v>
       </c>
       <c r="CF20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3533.7103537195435</v>
       </c>
       <c r="CG20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3498.3732501823479</v>
       </c>
       <c r="CH20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3463.3895176805245</v>
       </c>
       <c r="CI20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3428.7556225037192</v>
       </c>
       <c r="CJ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3394.4680662786818</v>
       </c>
       <c r="CK20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3360.5233856158948</v>
       </c>
       <c r="CL20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3326.9181517597358</v>
       </c>
       <c r="CM20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3293.6489702421386</v>
       </c>
       <c r="CN20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3260.712480539717</v>
       </c>
       <c r="CO20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3228.1053557343198</v>
       </c>
       <c r="CP20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3195.8243021769767</v>
       </c>
       <c r="CQ20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3163.866059155207</v>
       </c>
       <c r="CR20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3132.2273985636548</v>
       </c>
       <c r="CS20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3100.9051245780183</v>
       </c>
       <c r="CT20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3069.8960733322383</v>
       </c>
       <c r="CU20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3039.1971125989157</v>
       </c>
       <c r="CV20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>3008.8051414729266</v>
       </c>
       <c r="CW20" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>2978.7170900581973</v>
       </c>
       <c r="CX20" s="1">
-        <f t="shared" ref="CX20:ER20" si="31">CW20*(1+$AM$25)</f>
+        <f t="shared" ref="CX20:ER20" si="39">CW20*(1+$AM$25)</f>
         <v>2948.9299191576151</v>
       </c>
       <c r="CY20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2919.4406199660389</v>
       </c>
       <c r="CZ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2890.2462137663783</v>
       </c>
       <c r="DA20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2861.3437516287145</v>
       </c>
       <c r="DB20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2832.7303141124271</v>
       </c>
       <c r="DC20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2804.4030109713026</v>
       </c>
       <c r="DD20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2776.3589808615893</v>
       </c>
       <c r="DE20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2748.5953910529734</v>
       </c>
       <c r="DF20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2721.1094371424438</v>
       </c>
       <c r="DG20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2693.8983427710191</v>
       </c>
       <c r="DH20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2666.9593593433087</v>
       </c>
       <c r="DI20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2640.2897657498756</v>
       </c>
       <c r="DJ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2613.886868092377</v>
       </c>
       <c r="DK20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2587.7479994114533</v>
       </c>
       <c r="DL20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2561.8705194173385</v>
       </c>
       <c r="DM20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2536.2518142231652</v>
       </c>
       <c r="DN20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2510.8892960809335</v>
       </c>
       <c r="DO20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2485.780403120124</v>
       </c>
       <c r="DP20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2460.9225990889227</v>
       </c>
       <c r="DQ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2436.3133730980335</v>
       </c>
       <c r="DR20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2411.9502393670532</v>
       </c>
       <c r="DS20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2387.8307369733825</v>
       </c>
       <c r="DT20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2363.9524296036489</v>
       </c>
       <c r="DU20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2340.3129053076123</v>
       </c>
       <c r="DV20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2316.9097762545362</v>
       </c>
       <c r="DW20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2293.7406784919908</v>
       </c>
       <c r="DX20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2270.803271707071</v>
       </c>
       <c r="DY20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2248.0952389900003</v>
       </c>
       <c r="DZ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2225.6142866001005</v>
       </c>
       <c r="EA20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2203.3581437340995</v>
       </c>
       <c r="EB20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2181.3245622967584</v>
       </c>
       <c r="EC20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2159.5113166737906</v>
       </c>
       <c r="ED20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2137.9162035070526</v>
       </c>
       <c r="EE20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2116.5370414719819</v>
       </c>
       <c r="EF20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2095.3716710572621</v>
       </c>
       <c r="EG20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2074.4179543466894</v>
       </c>
       <c r="EH20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2053.6737748032224</v>
       </c>
       <c r="EI20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2033.1370370551901</v>
       </c>
       <c r="EJ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>2012.8056666846383</v>
       </c>
       <c r="EK20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1992.6776100177919</v>
       </c>
       <c r="EL20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1972.750833917614</v>
       </c>
       <c r="EM20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1953.0233255784378</v>
       </c>
       <c r="EN20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1933.4930923226534</v>
       </c>
       <c r="EO20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1914.1581613994269</v>
       </c>
       <c r="EP20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1895.0165797854327</v>
       </c>
       <c r="EQ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1876.0664139875782</v>
       </c>
       <c r="ER20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>1857.3057498477024</v>
       </c>
     </row>
@@ -3185,71 +3185,71 @@
         <v>552.70000000000005</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" ref="T21:Z21" si="32">554.4</f>
+        <f t="shared" ref="T21:Y21" si="40">554.4</f>
         <v>554.4</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>554.4</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>554.4</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>554.4</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>554.4</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>554.4</v>
       </c>
       <c r="Z21" s="5">
-        <f>552.7</f>
+        <f t="shared" ref="Z21:AJ21" si="41">552.7</f>
         <v>552.70000000000005</v>
       </c>
       <c r="AA21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AB21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AC21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AD21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AE21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AF21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AG21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AH21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AI21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
       <c r="AJ21" s="5">
-        <f>552.7</f>
+        <f t="shared" si="41"/>
         <v>552.70000000000005</v>
       </c>
     </row>
@@ -3266,95 +3266,95 @@
         <v>1.7171717171717173</v>
       </c>
       <c r="K22" s="7">
-        <f>K20/K21</f>
+        <f t="shared" ref="K22:P22" si="42">K20/K21</f>
         <v>1.3257575757575759</v>
       </c>
       <c r="L22" s="7">
-        <f>L20/L21</f>
+        <f t="shared" si="42"/>
         <v>1.6125541125541125</v>
       </c>
       <c r="M22" s="7">
-        <f>M20/M21</f>
+        <f t="shared" si="42"/>
         <v>1.0173160173160174</v>
       </c>
       <c r="N22" s="7">
-        <f>N20/N21</f>
+        <f t="shared" si="42"/>
         <v>1.691919191919192</v>
       </c>
       <c r="O22" s="7">
-        <f>O20/O21</f>
+        <f t="shared" si="42"/>
         <v>1.5349927849927851</v>
       </c>
       <c r="P22" s="7">
-        <f>P20/P21</f>
+        <f t="shared" si="42"/>
         <v>1.8563415958024243</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" ref="T22:Z22" si="33">T20/T21</f>
+        <f t="shared" ref="T22:Z22" si="43">T20/T21</f>
         <v>1.6107503607503608</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>1.727994227994228</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>2.4062049062049065</v>
       </c>
       <c r="W22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>4.5634920634920633</v>
       </c>
       <c r="X22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>5.5339105339105341</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>5.6475468975468974</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>7.8081402569205691</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AJ22" si="34">AA20/AA21</f>
+        <f t="shared" ref="AA22:AJ22" si="44">AA20/AA21</f>
         <v>8.5271406072010123</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>8.9709340294409294</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>9.3505993664292379</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>9.7134118607137125</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>9.8688182890962732</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>9.9934777881495158</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>10.084049527032805</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>10.174914262269716</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>10.266049905595432</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>10.357433264583694</v>
       </c>
     </row>
@@ -3367,11 +3367,11 @@
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
-        <f t="shared" ref="L24:M26" si="35">L3/H3-1</f>
+        <f t="shared" ref="L24:M26" si="45">L3/H3-1</f>
         <v>5.504587155963292E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>5.7135728542914155E-2</v>
       </c>
       <c r="N24" s="9"/>
@@ -3380,32 +3380,32 @@
         <v>1.1249999999999982E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24:P26" si="36">P3/L3-1</f>
+        <f t="shared" ref="P24:P26" si="46">P3/L3-1</f>
         <v>3.9613526570048352E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:Q26" si="37">Q3/M3-1</f>
+        <f t="shared" ref="Q24:Q26" si="47">Q3/M3-1</f>
         <v>-1</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24:R26" si="38">R3/N3-1</f>
+        <f t="shared" ref="R24:R26" si="48">R3/N3-1</f>
         <v>-1</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:X24" si="39">U3/T3-1</f>
+        <f t="shared" ref="U24:X24" si="49">U3/T3-1</f>
         <v>0.42482211594540997</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>8.9398280802292174E-2</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>8.6646126099045651E-2</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>8.0912863070539354E-2</v>
       </c>
       <c r="Y24" s="9">
@@ -3413,47 +3413,47 @@
         <v>6.4427383237364078E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AJ24" si="40">Z3/Y3-1</f>
+        <f t="shared" ref="Z24:AJ24" si="50">Z3/Y3-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3466,93 +3466,93 @@
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0.16225961538461542</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0.13063583815028901</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:O26" si="41">O4/K4-1</f>
+        <f t="shared" ref="O25:O26" si="51">O4/K4-1</f>
         <v>0.22876557191392988</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0.25336091003102368</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>-1</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9">
-        <f t="shared" ref="U25:X25" si="42">U4/T4-1</f>
+        <f t="shared" ref="U25:X25" si="52">U4/T4-1</f>
         <v>0.63382899628252787</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0.10693970420932875</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0.12264474134977732</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>5.675923100396707E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" ref="Y25:AJ26" si="43">Y4/X4-1</f>
+        <f t="shared" ref="Y25:AJ26" si="53">Y4/X4-1</f>
         <v>0.10280103956107411</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0.25</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" t="s">
@@ -3571,93 +3571,93 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>7.3801513877207681E-2</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>7.0182639031397542E-2</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>5.058365758754868E-2</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>8.0086156256119034E-2</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>-1</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10">
-        <f t="shared" ref="U26:X26" si="44">U5/T5-1</f>
+        <f t="shared" ref="U26:X26" si="54">U5/T5-1</f>
         <v>0.45793658584470398</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>9.2512792889846596E-2</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>9.3122149636386098E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>7.6450358008682384E-2</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>7.1387419473105229E-2</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>7.9205612045365692E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>5.5948724034855735E-2</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>3.6484956744428532E-2</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.9906340647923191E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.764685147014867E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.7813184103244728E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.5322333275749944E-2</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.2699636900695532E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.2719098080390845E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.2738646923175168E-2</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1.2758283067527243E-2</v>
       </c>
       <c r="AL26" t="s">
@@ -3672,28 +3672,28 @@
         <v>49</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N28" si="45">(H3-H6)/H3</f>
+        <f t="shared" ref="H27:N28" si="55">(H3-H6)/H3</f>
         <v>0.65570846075433231</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.67290419161676651</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.66149999999999998</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.67560386473429956</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.68232239792305882</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.6901408450704225</v>
       </c>
       <c r="O27" s="9">
@@ -3701,83 +3701,83 @@
         <v>0.6566131025957973</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:R27" si="46">(P3-P6)/P3</f>
+        <f t="shared" ref="P27:R27" si="56">(P3-P6)/P3</f>
         <v>0.67193308550185871</v>
       </c>
       <c r="Q27" s="9" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R27" s="9" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:X27" si="47">(T3-T6)/T3</f>
+        <f t="shared" ref="T27:X27" si="57">(T3-T6)/T3</f>
         <v>0.53155254869940516</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0.52181743757674992</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0.54279702412264219</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0.60089903181189486</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0.65886116442738318</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27:Y28" si="48">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y27:Y28" si="58">(Y3-Y6)/Y3</f>
         <v>0.67764621025425253</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AJ27" si="49">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z27:AJ27" si="59">(Z3-Z6)/Z3</f>
         <v>0.67999999999999994</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>0.68</v>
       </c>
       <c r="AL27" t="s">
@@ -3793,112 +3793,112 @@
         <v>50</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.30528846153846156</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.32601156069364162</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.26274065685164211</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.3391933815925543</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.32413087934560325</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.29465186680121092</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:P28" si="50">(O4-O7)/O4</f>
+        <f t="shared" ref="O28:P28" si="60">(O4-O7)/O4</f>
         <v>0.36958525345622117</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>0.4273927392739274</v>
       </c>
       <c r="Q28" s="9" t="e">
-        <f t="shared" ref="Q28:R28" si="51">(Q4-Q7)/Q4</f>
+        <f t="shared" ref="Q28:R28" si="61">(Q4-Q7)/Q4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R28" s="9" t="e">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:X28" si="52">(T4-T7)/T4</f>
+        <f t="shared" ref="T28:X28" si="62">(T4-T7)/T4</f>
         <v>0.19888475836431227</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>0.25255972696245732</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>0.29976019184652281</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>0.32224595666768385</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>0.32486283569159691</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>0.30610107357947108</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AJ28" si="53">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z28:AJ28" si="63">(Z4-Z7)/Z4</f>
         <v>0.35</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.34999999999999992</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="AL28" t="s">
@@ -3914,28 +3914,28 @@
         <v>51</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="54">H9/H5</f>
+        <f t="shared" ref="H29:N29" si="64">H9/H5</f>
         <v>0.59440706476030281</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>0.6113277241945414</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>0.58939176735613352</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>0.61190522811826908</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>0.61514860977948227</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>0.61550180917920394</v>
       </c>
       <c r="O29" s="9">
@@ -3943,83 +3943,83 @@
         <v>0.59590643274853805</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29:R29" si="55">P9/P5</f>
+        <f t="shared" ref="P29:R29" si="65">P9/P5</f>
         <v>0.6182015953589558</v>
       </c>
       <c r="Q29" s="9" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="9" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29:X29" si="56">T9/T5</f>
+        <f t="shared" ref="T29:X29" si="66">T9/T5</f>
         <v>0.47884558751349759</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>0.47401023431187717</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>0.4990755577468261</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>0.54941647403732308</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>0.59828209291363332</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="57">Y9/Y5</f>
+        <f t="shared" ref="Y29" si="67">Y9/Y5</f>
         <v>0.60828118889323424</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AJ29" si="58">Z9/Z5</f>
+        <f t="shared" ref="Z29:AJ29" si="68">Z9/Z5</f>
         <v>0.60864100890414707</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.60228520391912321</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.59827268965463354</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.59588463382836521</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.59405497486430814</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.59218150095012645</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.5909119822770571</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.59026976334710357</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.58962465153521859</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.58897665877159933</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.58832579737412216</v>
       </c>
       <c r="AL29" t="s">
@@ -4039,11 +4039,11 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:M30" si="59">L10/H10-1</f>
+        <f t="shared" ref="L30:M30" si="69">L10/H10-1</f>
         <v>5.8962264150941301E-4</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-2.7845036319612548E-2</v>
       </c>
       <c r="N30" s="9"/>
@@ -4052,32 +4052,32 @@
         <v>-8.8391278727165679E-3</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30" si="60">P10/L10-1</f>
+        <f t="shared" ref="P30" si="70">P10/L10-1</f>
         <v>8.2498526812020412E-3</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30" si="61">Q10/M10-1</f>
+        <f t="shared" ref="Q30" si="71">Q10/M10-1</f>
         <v>-1</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" ref="R30" si="62">R10/N10-1</f>
+        <f t="shared" ref="R30" si="72">R10/N10-1</f>
         <v>-1</v>
       </c>
       <c r="T30" s="9"/>
       <c r="U30" s="9">
-        <f t="shared" ref="U30:X30" si="63">U10/T10-1</f>
+        <f t="shared" ref="U30:X30" si="73">U10/T10-1</f>
         <v>0.72107186358099873</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>2.7954706298655374E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>4.2857142857142927E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="73"/>
         <v>8.5327611817131555E-2</v>
       </c>
       <c r="Y30" s="9">
@@ -4085,47 +4085,47 @@
         <v>-1.8248175182481452E-3</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AJ30" si="64">Z10/Y10-1</f>
+        <f t="shared" ref="Z30:AJ30" si="74">Z10/Y10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL30" t="s">
@@ -4141,28 +4141,28 @@
         <v>53</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="65">H13/H5</f>
+        <f t="shared" ref="H31:N31" si="75">H13/H5</f>
         <v>0.23780487804878048</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.30843422942745741</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.24185951259471636</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.27961621304092421</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.30719079578139979</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>0.3176537802323367</v>
       </c>
       <c r="O31" s="9">
@@ -4170,83 +4170,83 @@
         <v>0.27192982456140352</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" ref="P31:R31" si="66">P13/P5</f>
+        <f t="shared" ref="P31:R31" si="76">P13/P5</f>
         <v>0.30746918056562728</v>
       </c>
       <c r="Q31" s="9" t="e">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="9" t="e">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:X31" si="67">T13/T5</f>
+        <f t="shared" ref="T31:X31" si="77">T13/T5</f>
         <v>0.15794640227741238</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0.12469701050363588</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0.14100825835079503</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0.21085865704459605</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0.26260933326349972</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="68">Y13/Y5</f>
+        <f t="shared" ref="Y31" si="78">Y13/Y5</f>
         <v>0.28739734063355493</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31:AJ31" si="69">Z13/Z5</f>
+        <f t="shared" ref="Z31:AJ31" si="79">Z13/Z5</f>
         <v>0.30833429892694536</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.31504608882458968</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.31837330051471646</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32139522457444397</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32427912438624762</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32447656920186363</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32461036336810634</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.3246780466153884</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32474603474257036</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32481432649233249</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="79"/>
         <v>0.32488292056649809</v>
       </c>
       <c r="AL31" t="s">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM31" s="4">
         <f>Main!D3</f>
-        <v>140.47999999999999</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -4262,28 +4262,28 @@
         <v>27</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:N32" si="70">H18/H17</f>
+        <f t="shared" ref="H32:N32" si="80">H18/H17</f>
         <v>0.20733104238258879</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0.1975206611570248</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0.16757940854326397</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0.19420035149384884</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>5.8221872541306056E-2</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>0.16300675675675674</v>
       </c>
       <c r="O32" s="9">
@@ -4291,83 +4291,83 @@
         <v>0.18164435946462715</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" ref="P32:R32" si="71">P18/P17</f>
+        <f t="shared" ref="P32:R32" si="81">P18/P17</f>
         <v>0.19040247678018576</v>
       </c>
       <c r="Q32" s="9" t="e">
-        <f t="shared" si="71"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R32" s="9" t="e">
-        <f t="shared" si="71"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" ref="T32:X32" si="72">T18/T17</f>
+        <f t="shared" ref="T32:X32" si="82">T18/T17</f>
         <v>0.18282548476454294</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="82"/>
         <v>0.16737830913748933</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="82"/>
         <v>0.21788715486194477</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="82"/>
         <v>0.1891520768966701</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="82"/>
         <v>0.19343252950230888</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32" si="73">Y18/Y17</f>
+        <f t="shared" ref="Y32" si="83">Y18/Y17</f>
         <v>0.14225477141588994</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" ref="Z32:AJ32" si="74">Z18/Z17</f>
+        <f t="shared" ref="Z32:AJ32" si="84">Z18/Z17</f>
         <v>0.18</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="84"/>
         <v>0.18</v>
       </c>
       <c r="AL32" s="1" t="s">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AM32" s="10">
         <f>AM30/AM31-1</f>
-        <v>-0.43316132833590981</v>
+        <v>-0.36524913036770523</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
@@ -4383,28 +4383,28 @@
         <v>54</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:N33" si="75">H20/H5</f>
+        <f t="shared" ref="H33:N33" si="85">H20/H5</f>
         <v>0.14360807401177461</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>0.19536219987687256</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>0.15052221994675405</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>0.1750538476600744</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>0.10814956855225312</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>0.17863264140163779</v>
       </c>
       <c r="O33" s="9">
@@ -4412,83 +4412,83 @@
         <v>0.16588693957115011</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" ref="P33:R33" si="76">P20/P5</f>
+        <f t="shared" ref="P33:R33" si="86">P20/P5</f>
         <v>0.18600435097897028</v>
       </c>
       <c r="Q33" s="9" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R33" s="9" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" ref="T33:X33" si="77">T20/T5</f>
+        <f t="shared" ref="T33:X33" si="87">T20/T5</f>
         <v>8.766074408559929E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>6.4503097225962827E-2</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>8.2213731048933814E-2</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>0.14263967976546202</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>0.1606871628345467</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33" si="78">Y20/Y5</f>
+        <f t="shared" ref="Y33" si="88">Y20/Y5</f>
         <v>0.15306022682831444</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" ref="Z33:AJ33" si="79">Z20/Z5</f>
+        <f t="shared" ref="Z33:AJ33" si="89">Z20/Z5</f>
         <v>0.1954844246504045</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.2021739280162074</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20520899076042073</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20768275646369294</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20993695675411811</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20956279109037529</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20900743421653811</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20825689935963879</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20749430741328945</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20671948569222967</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="89"/>
         <v>0.20593225946595745</v>
       </c>
       <c r="AL33" t="s">

--- a/Financial Analysis/FI.xlsx
+++ b/Financial Analysis/FI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAC6815-1F12-4A07-9891-7528B2DD210B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A64CA2-3A6B-4E6B-A0D6-907B8C214BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9F0C41CC-C0DB-440C-AB99-1B4D33A170AF}"/>
   </bookViews>
@@ -220,10 +220,10 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Q225 8K</t>
-  </si>
-  <si>
     <t>Overvalued</t>
+  </si>
+  <si>
+    <t>Q325 8K</t>
   </si>
 </sst>
 </file>
@@ -746,17 +746,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>125.45</v>
+        <v>70.5</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="G3" s="3">
-        <v>45958</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,11 +764,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>552.7</f>
-        <v>552.70000000000005</v>
+        <f>541.8</f>
+        <v>541.79999999999995</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>69336.215000000011</v>
+        <v>38196.899999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>97924.215000000011</v>
+        <v>66784.899999999994</v>
       </c>
     </row>
   </sheetData>
@@ -967,6 +967,13 @@
       <c r="P3" s="5">
         <v>4304</v>
       </c>
+      <c r="Q3" s="5">
+        <v>4273</v>
+      </c>
+      <c r="R3" s="5">
+        <f>N3*1.02</f>
+        <v>4345.2</v>
+      </c>
       <c r="T3" s="5">
         <v>8573</v>
       </c>
@@ -986,48 +993,48 @@
         <v>16637</v>
       </c>
       <c r="Z3" s="5">
-        <f>Y3*1.04</f>
-        <v>17302.48</v>
+        <f>SUM(O3:R3)</f>
+        <v>16967.2</v>
       </c>
       <c r="AA3" s="5">
         <f>Z3*1.03</f>
-        <v>17821.554400000001</v>
+        <v>17476.216</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AD3" si="0">AA3*1.02</f>
-        <v>18177.985488000002</v>
+        <v>17825.740320000001</v>
       </c>
       <c r="AC3" s="5">
         <f t="shared" si="0"/>
-        <v>18541.545197760002</v>
+        <v>18182.255126399999</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" si="0"/>
-        <v>18912.376101715203</v>
+        <v>18545.900228928</v>
       </c>
       <c r="AE3" s="5">
         <f>AD3*1.01</f>
-        <v>19101.499862732355</v>
+        <v>18731.35923121728</v>
       </c>
       <c r="AF3" s="5">
         <f t="shared" ref="AF3:AJ3" si="1">AE3*1.01</f>
-        <v>19292.514861359679</v>
+        <v>18918.672823529454</v>
       </c>
       <c r="AG3" s="5">
         <f t="shared" si="1"/>
-        <v>19485.440009973277</v>
+        <v>19107.859551764748</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" si="1"/>
-        <v>19680.294410073009</v>
+        <v>19298.938147282395</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="1"/>
-        <v>19877.09735417374</v>
+        <v>19491.927528755219</v>
       </c>
       <c r="AJ3" s="5">
         <f t="shared" si="1"/>
-        <v>20075.868327715478</v>
+        <v>19686.846804042772</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1059,6 +1066,13 @@
       <c r="P4" s="5">
         <v>1212</v>
       </c>
+      <c r="Q4" s="5">
+        <v>990</v>
+      </c>
+      <c r="R4" s="5">
+        <f>N4*1.02</f>
+        <v>1010.82</v>
+      </c>
       <c r="T4" s="5">
         <v>1614</v>
       </c>
@@ -1078,48 +1092,48 @@
         <v>3819</v>
       </c>
       <c r="Z4" s="5">
-        <f>Y4*1.25</f>
-        <v>4773.75</v>
+        <f>SUM(O4:R4)</f>
+        <v>4297.82</v>
       </c>
       <c r="AA4" s="5">
-        <f>Z4*1.15</f>
-        <v>5489.8125</v>
+        <f>Z4*1.05</f>
+        <v>4512.7110000000002</v>
       </c>
       <c r="AB4" s="5">
-        <f>AA4*1.09</f>
-        <v>5983.8956250000001</v>
+        <f>AA4*1.04</f>
+        <v>4693.2194400000008</v>
       </c>
       <c r="AC4" s="5">
-        <f>AB4*1.06</f>
-        <v>6342.9293625</v>
+        <f>AB4*1.03</f>
+        <v>4834.0160232000007</v>
       </c>
       <c r="AD4" s="5">
-        <f>AC4*1.05</f>
-        <v>6660.075830625</v>
+        <f>AC4*1.02</f>
+        <v>4930.6963436640008</v>
       </c>
       <c r="AE4" s="5">
-        <f>AD4*1.04</f>
-        <v>6926.4788638500004</v>
+        <f t="shared" ref="AE4:AJ4" si="2">AD4*1.02</f>
+        <v>5029.3102705372812</v>
       </c>
       <c r="AF4" s="5">
-        <f>AE4*1.03</f>
-        <v>7134.2732297655002</v>
+        <f t="shared" si="2"/>
+        <v>5129.8964759480268</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" ref="AG4:AJ4" si="2">AF4*1.02</f>
-        <v>7276.9586943608101</v>
+        <f t="shared" si="2"/>
+        <v>5232.4944054669877</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>7422.4978682480269</v>
+        <v>5337.144293576328</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>7570.9478256129878</v>
+        <v>5443.8871794478546</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>7722.3667821252475</v>
+        <v>5552.7649230368115</v>
       </c>
     </row>
     <row r="5" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1158,73 +1172,81 @@
         <f t="shared" si="3"/>
         <v>5516</v>
       </c>
+      <c r="Q5" s="8">
+        <f t="shared" ref="Q5:R5" si="4">Q3+Q4</f>
+        <v>5263</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" si="4"/>
+        <v>5356.0199999999995</v>
+      </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:Y5" si="4">T3+T4</f>
+        <f t="shared" ref="T5:Y5" si="5">T3+T4</f>
         <v>10187</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14852</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16226</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17737</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19093</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20456</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5:AJ5" si="5">Z3+Z4</f>
-        <v>22076.23</v>
+        <f t="shared" ref="Z5:AJ5" si="6">Z3+Z4</f>
+        <v>21265.02</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="5"/>
-        <v>23311.366900000001</v>
+        <f t="shared" si="6"/>
+        <v>21988.927</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="5"/>
-        <v>24161.881113000003</v>
+        <f t="shared" si="6"/>
+        <v>22518.959760000002</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="5"/>
-        <v>24884.474560260001</v>
+        <f t="shared" si="6"/>
+        <v>23016.271149600001</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="5"/>
-        <v>25572.451932340202</v>
+        <f t="shared" si="6"/>
+        <v>23476.596572592</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="5"/>
-        <v>26027.978726582354</v>
+        <f t="shared" si="6"/>
+        <v>23760.669501754561</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="5"/>
-        <v>26426.788091125178</v>
+        <f t="shared" si="6"/>
+        <v>24048.56929947748</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="5"/>
-        <v>26762.398704334089</v>
+        <f t="shared" si="6"/>
+        <v>24340.353957231735</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="5"/>
-        <v>27102.792278321038</v>
+        <f t="shared" si="6"/>
+        <v>24636.082440858721</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="5"/>
-        <v>27448.045179786728</v>
+        <f t="shared" si="6"/>
+        <v>24935.814708203074</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="5"/>
-        <v>27798.235109840723</v>
+        <f t="shared" si="6"/>
+        <v>25239.611727079584</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1247,7 +1269,7 @@
         <v>1346</v>
       </c>
       <c r="N6" s="5">
-        <f t="shared" ref="N6:N7" si="6">Y6-M6-L6-K6</f>
+        <f t="shared" ref="N6:N7" si="7">Y6-M6-L6-K6</f>
         <v>1320</v>
       </c>
       <c r="O6" s="5">
@@ -1256,6 +1278,13 @@
       <c r="P6" s="5">
         <v>1412</v>
       </c>
+      <c r="Q6" s="5">
+        <v>1486</v>
+      </c>
+      <c r="R6" s="5">
+        <f>R3*0.34</f>
+        <v>1477.3679999999999</v>
+      </c>
       <c r="T6" s="5">
         <v>4016</v>
       </c>
@@ -1275,48 +1304,48 @@
         <v>5363</v>
       </c>
       <c r="Z6" s="5">
-        <f>Z3*0.32</f>
-        <v>5536.7936</v>
+        <f t="shared" ref="Z6:Z7" si="8">SUM(O6:R6)</f>
+        <v>5764.3680000000004</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AJ6" si="7">AA3*0.32</f>
-        <v>5702.8974080000007</v>
+        <f t="shared" ref="AA6:AJ6" si="9">AA3*0.32</f>
+        <v>5592.3891199999998</v>
       </c>
       <c r="AB6" s="5">
-        <f t="shared" si="7"/>
-        <v>5816.9553561600005</v>
+        <f t="shared" si="9"/>
+        <v>5704.2369024</v>
       </c>
       <c r="AC6" s="5">
-        <f t="shared" si="7"/>
-        <v>5933.2944632832005</v>
+        <f t="shared" si="9"/>
+        <v>5818.3216404479999</v>
       </c>
       <c r="AD6" s="5">
-        <f t="shared" si="7"/>
-        <v>6051.9603525488646</v>
+        <f t="shared" si="9"/>
+        <v>5934.6880732569598</v>
       </c>
       <c r="AE6" s="5">
-        <f t="shared" si="7"/>
-        <v>6112.479956074354</v>
+        <f t="shared" si="9"/>
+        <v>5994.0349539895296</v>
       </c>
       <c r="AF6" s="5">
-        <f t="shared" si="7"/>
-        <v>6173.6047556350977</v>
+        <f t="shared" si="9"/>
+        <v>6053.9753035294252</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" si="7"/>
-        <v>6235.3408031914487</v>
+        <f t="shared" si="9"/>
+        <v>6114.51505656472</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="7"/>
-        <v>6297.6942112233628</v>
+        <f t="shared" si="9"/>
+        <v>6175.6602071303669</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="7"/>
-        <v>6360.6711533355974</v>
+        <f t="shared" si="9"/>
+        <v>6237.4168092016698</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="7"/>
-        <v>6424.2778648689527</v>
+        <f t="shared" si="9"/>
+        <v>6299.7909772936873</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
@@ -1339,7 +1368,7 @@
         <v>661</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>699</v>
       </c>
       <c r="O7" s="5">
@@ -1348,6 +1377,13 @@
       <c r="P7" s="5">
         <v>694</v>
       </c>
+      <c r="Q7" s="5">
+        <v>679</v>
+      </c>
+      <c r="R7" s="5">
+        <f>R4*0.72</f>
+        <v>727.79039999999998</v>
+      </c>
       <c r="T7" s="5">
         <v>1293</v>
       </c>
@@ -1367,48 +1403,48 @@
         <v>2650</v>
       </c>
       <c r="Z7" s="5">
-        <f>Z4*0.65</f>
-        <v>3102.9375</v>
+        <f t="shared" si="8"/>
+        <v>2784.7903999999999</v>
       </c>
       <c r="AA7" s="5">
-        <f t="shared" ref="AA7:AJ7" si="8">AA4*0.65</f>
-        <v>3568.3781250000002</v>
+        <f t="shared" ref="AA7:AJ7" si="10">AA4*0.65</f>
+        <v>2933.2621500000005</v>
       </c>
       <c r="AB7" s="5">
-        <f t="shared" si="8"/>
-        <v>3889.5321562500003</v>
+        <f t="shared" si="10"/>
+        <v>3050.5926360000008</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" si="8"/>
-        <v>4122.9040856250003</v>
+        <f t="shared" si="10"/>
+        <v>3142.1104150800006</v>
       </c>
       <c r="AD7" s="5">
-        <f t="shared" si="8"/>
-        <v>4329.0492899062501</v>
+        <f t="shared" si="10"/>
+        <v>3204.9526233816005</v>
       </c>
       <c r="AE7" s="5">
-        <f t="shared" si="8"/>
-        <v>4502.2112615025007</v>
+        <f t="shared" si="10"/>
+        <v>3269.0516758492331</v>
       </c>
       <c r="AF7" s="5">
-        <f t="shared" si="8"/>
-        <v>4637.2775993475752</v>
+        <f t="shared" si="10"/>
+        <v>3334.4327093662178</v>
       </c>
       <c r="AG7" s="5">
-        <f t="shared" si="8"/>
-        <v>4730.023151334527</v>
+        <f t="shared" si="10"/>
+        <v>3401.1213635535423</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" si="8"/>
-        <v>4824.6236143612177</v>
+        <f t="shared" si="10"/>
+        <v>3469.1437908246135</v>
       </c>
       <c r="AI7" s="5">
-        <f t="shared" si="8"/>
-        <v>4921.1160866484424</v>
+        <f t="shared" si="10"/>
+        <v>3538.5266666411057</v>
       </c>
       <c r="AJ7" s="5">
-        <f t="shared" si="8"/>
-        <v>5019.5384083814106</v>
+        <f t="shared" si="10"/>
+        <v>3609.2971999739275</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
@@ -1424,96 +1460,104 @@
         <v>1894</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" ref="K8:P8" si="9">K6+K7</f>
+        <f t="shared" ref="K8:P8" si="11">K6+K7</f>
         <v>2005</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1982</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2007</v>
       </c>
       <c r="N8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2019</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2073</v>
       </c>
       <c r="P8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2106</v>
       </c>
+      <c r="Q8" s="5">
+        <f t="shared" ref="Q8:R8" si="12">Q6+Q7</f>
+        <v>2165</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="12"/>
+        <v>2205.1583999999998</v>
+      </c>
       <c r="T8" s="5">
-        <f t="shared" ref="T8:Z8" si="10">T6+T7</f>
+        <f t="shared" ref="T8:Z8" si="13">T6+T7</f>
         <v>5309</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7812</v>
       </c>
       <c r="V8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>8128</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7992</v>
       </c>
       <c r="X8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7670</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>8013</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" si="10"/>
-        <v>8639.7311000000009</v>
+        <f t="shared" si="13"/>
+        <v>8549.1584000000003</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AJ8" si="11">AA6+AA7</f>
-        <v>9271.275533</v>
+        <f t="shared" ref="AA8:AJ8" si="14">AA6+AA7</f>
+        <v>8525.6512700000003</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" si="11"/>
-        <v>9706.4875124099999</v>
+        <f t="shared" si="14"/>
+        <v>8754.8295384000012</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="11"/>
-        <v>10056.1985489082</v>
+        <f t="shared" si="14"/>
+        <v>8960.432055528001</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" si="11"/>
-        <v>10381.009642455116</v>
+        <f t="shared" si="14"/>
+        <v>9139.6406966385603</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="11"/>
-        <v>10614.691217576856</v>
+        <f t="shared" si="14"/>
+        <v>9263.0866298387627</v>
       </c>
       <c r="AF8" s="5">
-        <f t="shared" si="11"/>
-        <v>10810.882354982674</v>
+        <f t="shared" si="14"/>
+        <v>9388.408012895643</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="11"/>
-        <v>10965.363954525976</v>
+        <f t="shared" si="14"/>
+        <v>9515.6364201182623</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" si="11"/>
-        <v>11122.317825584581</v>
+        <f t="shared" si="14"/>
+        <v>9644.8039979549794</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" si="11"/>
-        <v>11281.78723998404</v>
+        <f t="shared" si="14"/>
+        <v>9775.943475842776</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="11"/>
-        <v>11443.816273250362</v>
+        <f t="shared" si="14"/>
+        <v>9909.0881772676148</v>
       </c>
     </row>
     <row r="9" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1529,96 +1573,104 @@
         <v>2979</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" ref="K9:P9" si="12">K5-K8</f>
+        <f t="shared" ref="K9:P9" si="15">K5-K8</f>
         <v>2878</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3125</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3208</v>
       </c>
       <c r="N9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3232</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3057</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3410</v>
       </c>
+      <c r="Q9" s="8">
+        <f t="shared" ref="Q9:R9" si="16">Q5-Q8</f>
+        <v>3098</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" si="16"/>
+        <v>3150.8615999999997</v>
+      </c>
       <c r="T9" s="8">
-        <f t="shared" ref="T9:Z9" si="13">T5-T8</f>
+        <f t="shared" ref="T9:Z9" si="17">T5-T8</f>
         <v>4878</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>7040</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>8098</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>9745</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11423</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12443</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" si="13"/>
-        <v>13436.498899999999</v>
+        <f t="shared" si="17"/>
+        <v>12715.8616</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AJ9" si="14">AA5-AA8</f>
-        <v>14040.091367000001</v>
+        <f t="shared" ref="AA9:AJ9" si="18">AA5-AA8</f>
+        <v>13463.275729999999</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="14"/>
-        <v>14455.393600590003</v>
+        <f t="shared" si="18"/>
+        <v>13764.1302216</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="14"/>
-        <v>14828.276011351802</v>
+        <f t="shared" si="18"/>
+        <v>14055.839094072</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" si="14"/>
-        <v>15191.442289885086</v>
+        <f t="shared" si="18"/>
+        <v>14336.955875953439</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" si="14"/>
-        <v>15413.287509005499</v>
+        <f t="shared" si="18"/>
+        <v>14497.582871915798</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="14"/>
-        <v>15615.905736142504</v>
+        <f t="shared" si="18"/>
+        <v>14660.161286581837</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="14"/>
-        <v>15797.034749808114</v>
+        <f t="shared" si="18"/>
+        <v>14824.717537113473</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="14"/>
-        <v>15980.474452736456</v>
+        <f t="shared" si="18"/>
+        <v>14991.278442903742</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="14"/>
-        <v>16166.257939802688</v>
+        <f t="shared" si="18"/>
+        <v>15159.871232360298</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="14"/>
-        <v>16354.418836590361</v>
+        <f t="shared" si="18"/>
+        <v>15330.523549811969</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1641,7 +1693,7 @@
         <v>1606</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" ref="N10:N11" si="15">Y10-M10-L10-K10</f>
+        <f t="shared" ref="N10:N11" si="19">Y10-M10-L10-K10</f>
         <v>1564</v>
       </c>
       <c r="O10" s="5">
@@ -1650,6 +1702,13 @@
       <c r="P10" s="5">
         <v>1711</v>
       </c>
+      <c r="Q10" s="5">
+        <v>1762</v>
+      </c>
+      <c r="R10" s="5">
+        <f>N10*1.14</f>
+        <v>1782.9599999999998</v>
+      </c>
       <c r="T10" s="5">
         <v>3284</v>
       </c>
@@ -1669,48 +1728,48 @@
         <v>6564</v>
       </c>
       <c r="Z10" s="5">
-        <f>Y10*1.01</f>
-        <v>6629.64</v>
+        <f t="shared" ref="Z10:Z11" si="20">SUM(O10:R10)</f>
+        <v>6937.96</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" ref="AA10:AJ10" si="16">Z10*1.01</f>
-        <v>6695.9364000000005</v>
+        <f t="shared" ref="AA10:AJ10" si="21">Z10*1.01</f>
+        <v>7007.3396000000002</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" si="16"/>
-        <v>6762.8957640000008</v>
+        <f t="shared" si="21"/>
+        <v>7077.412996</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="16"/>
-        <v>6830.5247216400012</v>
+        <f t="shared" si="21"/>
+        <v>7148.1871259600002</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="16"/>
-        <v>6898.8299688564011</v>
+        <f t="shared" si="21"/>
+        <v>7219.6689972196</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="16"/>
-        <v>6967.8182685449656</v>
+        <f t="shared" si="21"/>
+        <v>7291.8656871917965</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="16"/>
-        <v>7037.496451230415</v>
+        <f t="shared" si="21"/>
+        <v>7364.7843440637143</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="16"/>
-        <v>7107.8714157427194</v>
+        <f t="shared" si="21"/>
+        <v>7438.4321875043515</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="16"/>
-        <v>7178.9501299001467</v>
+        <f t="shared" si="21"/>
+        <v>7512.816509379395</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="16"/>
-        <v>7250.7396311991479</v>
+        <f t="shared" si="21"/>
+        <v>7587.9446744731895</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="16"/>
-        <v>7323.2470275111391</v>
+        <f t="shared" si="21"/>
+        <v>7663.8241212179219</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1733,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O11" s="5">
@@ -1742,6 +1801,12 @@
       <c r="P11" s="5">
         <v>3</v>
       </c>
+      <c r="Q11" s="5">
+        <v>-100</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
       <c r="T11" s="5">
         <v>-15</v>
       </c>
@@ -1761,7 +1826,8 @@
         <v>0</v>
       </c>
       <c r="Z11" s="5">
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-117</v>
       </c>
       <c r="AA11" s="5">
         <v>0</v>
@@ -1807,96 +1873,104 @@
         <v>1476</v>
       </c>
       <c r="K12" s="5">
-        <f t="shared" ref="K12:P12" si="17">SUM(K10:K11)</f>
+        <f t="shared" ref="K12:P12" si="22">SUM(K10:K11)</f>
         <v>1697</v>
       </c>
       <c r="L12" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1697</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1606</v>
       </c>
       <c r="N12" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1564</v>
       </c>
       <c r="O12" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1662</v>
       </c>
       <c r="P12" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1714</v>
       </c>
+      <c r="Q12" s="5">
+        <f t="shared" ref="Q12:R12" si="23">SUM(Q10:Q11)</f>
+        <v>1662</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="23"/>
+        <v>1782.9599999999998</v>
+      </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:Z12" si="18">SUM(T10:T11)</f>
+        <f t="shared" ref="T12:Z12" si="24">SUM(T10:T11)</f>
         <v>3269</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>5188</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>5810</v>
       </c>
       <c r="W12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6005</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6409</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6564</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="18"/>
-        <v>6629.64</v>
+        <f t="shared" si="24"/>
+        <v>6820.96</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" ref="AA12:AJ12" si="19">SUM(AA10:AA11)</f>
-        <v>6695.9364000000005</v>
+        <f t="shared" ref="AA12:AJ12" si="25">SUM(AA10:AA11)</f>
+        <v>7007.3396000000002</v>
       </c>
       <c r="AB12" s="5">
-        <f t="shared" si="19"/>
-        <v>6762.8957640000008</v>
+        <f t="shared" si="25"/>
+        <v>7077.412996</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" si="19"/>
-        <v>6830.5247216400012</v>
+        <f t="shared" si="25"/>
+        <v>7148.1871259600002</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="19"/>
-        <v>6898.8299688564011</v>
+        <f t="shared" si="25"/>
+        <v>7219.6689972196</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="19"/>
-        <v>6967.8182685449656</v>
+        <f t="shared" si="25"/>
+        <v>7291.8656871917965</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="19"/>
-        <v>7037.496451230415</v>
+        <f t="shared" si="25"/>
+        <v>7364.7843440637143</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="19"/>
-        <v>7107.8714157427194</v>
+        <f t="shared" si="25"/>
+        <v>7438.4321875043515</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="19"/>
-        <v>7178.9501299001467</v>
+        <f t="shared" si="25"/>
+        <v>7512.816509379395</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="19"/>
-        <v>7250.7396311991479</v>
+        <f t="shared" si="25"/>
+        <v>7587.9446744731895</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="19"/>
-        <v>7323.2470275111391</v>
+        <f t="shared" si="25"/>
+        <v>7663.8241212179219</v>
       </c>
     </row>
     <row r="13" spans="2:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1912,96 +1986,104 @@
         <v>1503</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" ref="K13:P13" si="20">K9-K12</f>
+        <f t="shared" ref="K13:P13" si="26">K9-K12</f>
         <v>1181</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1428</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1602</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1668</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1395</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1696</v>
       </c>
+      <c r="Q13" s="8">
+        <f t="shared" ref="Q13:R13" si="27">Q9-Q12</f>
+        <v>1436</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" si="27"/>
+        <v>1367.9015999999999</v>
+      </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13:Z13" si="21">T9-T12</f>
+        <f t="shared" ref="T13:Z13" si="28">T9-T12</f>
         <v>1609</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>1852</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>2288</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>3740</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>5014</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>5879</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="21"/>
-        <v>6806.8588999999984</v>
+        <f t="shared" si="28"/>
+        <v>5894.9016000000001</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AJ13" si="22">AA9-AA12</f>
-        <v>7344.1549670000004</v>
+        <f t="shared" ref="AA13:AJ13" si="29">AA9-AA12</f>
+        <v>6455.9361299999991</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="22"/>
-        <v>7692.4978365900024</v>
+        <f t="shared" si="29"/>
+        <v>6686.7172256000003</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="22"/>
-        <v>7997.7512897118004</v>
+        <f t="shared" si="29"/>
+        <v>6907.6519681119998</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="22"/>
-        <v>8292.612321028686</v>
+        <f t="shared" si="29"/>
+        <v>7117.2868787338393</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="22"/>
-        <v>8445.4692404605339</v>
+        <f t="shared" si="29"/>
+        <v>7205.7171847240015</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="22"/>
-        <v>8578.4092849120898</v>
+        <f t="shared" si="29"/>
+        <v>7295.3769425181226</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="22"/>
-        <v>8689.1633340653934</v>
+        <f t="shared" si="29"/>
+        <v>7386.2853496091211</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="22"/>
-        <v>8801.5243228363106</v>
+        <f t="shared" si="29"/>
+        <v>7478.4619335243469</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="22"/>
-        <v>8915.5183086035395</v>
+        <f t="shared" si="29"/>
+        <v>7571.9265578871082</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="22"/>
-        <v>9031.1718090792219</v>
+        <f t="shared" si="29"/>
+        <v>7666.6994285940473</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
@@ -2024,7 +2106,7 @@
         <v>326</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" ref="N14:N15" si="23">Y14-M14-L14-K14</f>
+        <f t="shared" ref="N14:N15" si="30">Y14-M14-L14-K14</f>
         <v>323</v>
       </c>
       <c r="O14" s="5">
@@ -2032,6 +2114,12 @@
       </c>
       <c r="P14" s="5">
         <v>365</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>422</v>
+      </c>
+      <c r="R14" s="5">
+        <v>450</v>
       </c>
       <c r="T14" s="5">
         <f>473+47</f>
@@ -2053,48 +2141,48 @@
         <v>1195</v>
       </c>
       <c r="Z14" s="5">
-        <f>Y14*1.03</f>
-        <v>1230.8500000000001</v>
+        <f t="shared" ref="Z14:Z15" si="31">SUM(O14:R14)</f>
+        <v>1568</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" ref="AA14:AJ14" si="24">Z14*1.03</f>
-        <v>1267.7755000000002</v>
+        <f t="shared" ref="AA14:AJ14" si="32">Z14*1.03</f>
+        <v>1615.04</v>
       </c>
       <c r="AB14" s="5">
-        <f t="shared" si="24"/>
-        <v>1305.8087650000002</v>
+        <f t="shared" si="32"/>
+        <v>1663.4911999999999</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="24"/>
-        <v>1344.9830279500002</v>
+        <f t="shared" si="32"/>
+        <v>1713.3959359999999</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="24"/>
-        <v>1385.3325187885002</v>
+        <f t="shared" si="32"/>
+        <v>1764.7978140799999</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="24"/>
-        <v>1426.8924943521554</v>
+        <f t="shared" si="32"/>
+        <v>1817.7417485023998</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="24"/>
-        <v>1469.6992691827202</v>
+        <f t="shared" si="32"/>
+        <v>1872.2740009574718</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="24"/>
-        <v>1513.7902472582018</v>
+        <f t="shared" si="32"/>
+        <v>1928.4422209861959</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="24"/>
-        <v>1559.2039546759479</v>
+        <f t="shared" si="32"/>
+        <v>1986.2954876157819</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="24"/>
-        <v>1605.9800733162265</v>
+        <f t="shared" si="32"/>
+        <v>2045.8843522442553</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="24"/>
-        <v>1654.1594755157132</v>
+        <f t="shared" si="32"/>
+        <v>2107.2608828115831</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.3">
@@ -2117,7 +2205,7 @@
         <v>5</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>161</v>
       </c>
       <c r="O15" s="5">
@@ -2126,6 +2214,12 @@
       <c r="P15" s="5">
         <v>39</v>
       </c>
+      <c r="Q15" s="5">
+        <v>50</v>
+      </c>
+      <c r="R15" s="5">
+        <v>50</v>
+      </c>
       <c r="T15" s="5">
         <v>6</v>
       </c>
@@ -2145,48 +2239,48 @@
         <v>178</v>
       </c>
       <c r="Z15" s="5">
-        <f>Y15*1.02</f>
-        <v>181.56</v>
+        <f t="shared" si="31"/>
+        <v>157</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" ref="AA15:AJ15" si="25">Z15*1.02</f>
-        <v>185.19120000000001</v>
+        <f t="shared" ref="AA15:AJ15" si="33">Z15*1.02</f>
+        <v>160.14000000000001</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" si="25"/>
-        <v>188.89502400000001</v>
+        <f t="shared" si="33"/>
+        <v>163.34280000000001</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="25"/>
-        <v>192.67292448000001</v>
+        <f t="shared" si="33"/>
+        <v>166.609656</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="25"/>
-        <v>196.52638296960001</v>
+        <f t="shared" si="33"/>
+        <v>169.94184912</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="25"/>
-        <v>200.45691062899201</v>
+        <f t="shared" si="33"/>
+        <v>173.34068610240001</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="25"/>
-        <v>204.46604884157185</v>
+        <f t="shared" si="33"/>
+        <v>176.80749982444803</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="25"/>
-        <v>208.55536981840328</v>
+        <f t="shared" si="33"/>
+        <v>180.343649820937</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="25"/>
-        <v>212.72647721477134</v>
+        <f t="shared" si="33"/>
+        <v>183.95052281735573</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="25"/>
-        <v>216.98100675906676</v>
+        <f t="shared" si="33"/>
+        <v>187.62953327370286</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="25"/>
-        <v>221.32062689424811</v>
+        <f t="shared" si="33"/>
+        <v>191.38212393917692</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.3">
@@ -2202,96 +2296,104 @@
         <v>293</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16:P16" si="26">SUM(K14:K15)</f>
+        <f t="shared" ref="K16:P16" si="34">SUM(K14:K15)</f>
         <v>268</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>290</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>331</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>484</v>
       </c>
       <c r="O16" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>349</v>
       </c>
       <c r="P16" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>404</v>
       </c>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:R16" si="35">SUM(Q14:Q15)</f>
+        <v>472</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="35"/>
+        <v>500</v>
+      </c>
       <c r="T16" s="5">
-        <f t="shared" ref="T16:Z16" si="27">SUM(T14:T15)</f>
+        <f t="shared" ref="T16:Z16" si="36">SUM(T14:T15)</f>
         <v>526</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>681</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>622</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>827</v>
       </c>
       <c r="X16" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>1116</v>
       </c>
       <c r="Y16" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>1373</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" si="27"/>
-        <v>1412.41</v>
+        <f t="shared" si="36"/>
+        <v>1725</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AJ16" si="28">SUM(AA14:AA15)</f>
-        <v>1452.9667000000002</v>
+        <f t="shared" ref="AA16:AJ16" si="37">SUM(AA14:AA15)</f>
+        <v>1775.18</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" si="28"/>
-        <v>1494.7037890000001</v>
+        <f t="shared" si="37"/>
+        <v>1826.8339999999998</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="28"/>
-        <v>1537.6559524300001</v>
+        <f t="shared" si="37"/>
+        <v>1880.005592</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="28"/>
-        <v>1581.8589017581003</v>
+        <f t="shared" si="37"/>
+        <v>1934.7396631999998</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="28"/>
-        <v>1627.3494049811475</v>
+        <f t="shared" si="37"/>
+        <v>1991.0824346047998</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="28"/>
-        <v>1674.165318024292</v>
+        <f t="shared" si="37"/>
+        <v>2049.0815007819197</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="28"/>
-        <v>1722.3456170766051</v>
+        <f t="shared" si="37"/>
+        <v>2108.7858708071331</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="28"/>
-        <v>1771.9304318907193</v>
+        <f t="shared" si="37"/>
+        <v>2170.2460104331376</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="28"/>
-        <v>1822.9610800752932</v>
+        <f t="shared" si="37"/>
+        <v>2233.513885517958</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="28"/>
-        <v>1875.4801024099613</v>
+        <f t="shared" si="37"/>
+        <v>2298.6430067507599</v>
       </c>
     </row>
     <row r="17" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2307,96 +2409,104 @@
         <v>1210</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" ref="K17:P17" si="29">K13-K16</f>
+        <f t="shared" ref="K17:P17" si="38">K13-K16</f>
         <v>913</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1138</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1271</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1184</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1046</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1292</v>
       </c>
+      <c r="Q17" s="8">
+        <f t="shared" ref="Q17:R17" si="39">Q13-Q16</f>
+        <v>964</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="39"/>
+        <v>867.90159999999992</v>
+      </c>
       <c r="T17" s="8">
-        <f t="shared" ref="T17:Z17" si="30">T13-T16</f>
+        <f t="shared" ref="T17:Z17" si="40">T13-T16</f>
         <v>1083</v>
       </c>
       <c r="U17" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>1171</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>1666</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>2913</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>3898</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>4506</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" si="30"/>
-        <v>5394.4488999999985</v>
+        <f t="shared" si="40"/>
+        <v>4169.9016000000001</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" ref="AA17:AJ17" si="31">AA13-AA16</f>
-        <v>5891.1882670000005</v>
+        <f t="shared" ref="AA17:AJ17" si="41">AA13-AA16</f>
+        <v>4680.7561299999988</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="31"/>
-        <v>6197.7940475900023</v>
+        <f t="shared" si="41"/>
+        <v>4859.8832256000005</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="31"/>
-        <v>6460.0953372818003</v>
+        <f t="shared" si="41"/>
+        <v>5027.6463761119994</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="31"/>
-        <v>6710.7534192705862</v>
+        <f t="shared" si="41"/>
+        <v>5182.5472155338393</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="31"/>
-        <v>6818.1198354793869</v>
+        <f t="shared" si="41"/>
+        <v>5214.6347501192013</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="31"/>
-        <v>6904.2439668877978</v>
+        <f t="shared" si="41"/>
+        <v>5246.2954417362034</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="31"/>
-        <v>6966.8177169887886</v>
+        <f t="shared" si="41"/>
+        <v>5277.4994788019885</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="31"/>
-        <v>7029.5938909455908</v>
+        <f t="shared" si="41"/>
+        <v>5308.2159230912093</v>
       </c>
       <c r="AI17" s="8">
-        <f t="shared" si="31"/>
-        <v>7092.557228528246</v>
+        <f t="shared" si="41"/>
+        <v>5338.4126723691497</v>
       </c>
       <c r="AJ17" s="8">
-        <f t="shared" si="31"/>
-        <v>7155.6917066692604</v>
+        <f t="shared" si="41"/>
+        <v>5368.0564218432874</v>
       </c>
     </row>
     <row r="18" spans="2:148" x14ac:dyDescent="0.3">
@@ -2419,7 +2529,7 @@
         <v>74</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" ref="N18:N19" si="32">Y18-M18-L18-K18</f>
+        <f t="shared" ref="N18:N19" si="42">Y18-M18-L18-K18</f>
         <v>193</v>
       </c>
       <c r="O18" s="5">
@@ -2428,6 +2538,13 @@
       <c r="P18" s="5">
         <v>246</v>
       </c>
+      <c r="Q18" s="5">
+        <v>173</v>
+      </c>
+      <c r="R18" s="5">
+        <f>R17*0.18</f>
+        <v>156.22228799999999</v>
+      </c>
       <c r="T18" s="5">
         <v>198</v>
       </c>
@@ -2447,48 +2564,48 @@
         <v>641</v>
       </c>
       <c r="Z18" s="5">
-        <f>Z17*0.18</f>
-        <v>971.00080199999968</v>
+        <f t="shared" ref="Z18:Z19" si="43">SUM(O18:R18)</f>
+        <v>765.22228799999993</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" ref="AA18:AJ18" si="33">AA17*0.18</f>
-        <v>1060.4138880600001</v>
+        <f t="shared" ref="AA18:AJ18" si="44">AA17*0.18</f>
+        <v>842.53610339999977</v>
       </c>
       <c r="AB18" s="5">
-        <f t="shared" si="33"/>
-        <v>1115.6029285662003</v>
+        <f t="shared" si="44"/>
+        <v>874.7789806080001</v>
       </c>
       <c r="AC18" s="5">
-        <f t="shared" si="33"/>
-        <v>1162.817160710724</v>
+        <f t="shared" si="44"/>
+        <v>904.97634770015986</v>
       </c>
       <c r="AD18" s="5">
-        <f t="shared" si="33"/>
-        <v>1207.9356154687055</v>
+        <f t="shared" si="44"/>
+        <v>932.858498796091</v>
       </c>
       <c r="AE18" s="5">
-        <f t="shared" si="33"/>
-        <v>1227.2615703862896</v>
+        <f t="shared" si="44"/>
+        <v>938.63425502145617</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" si="33"/>
-        <v>1242.7639140398035</v>
+        <f t="shared" si="44"/>
+        <v>944.33317951251661</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="33"/>
-        <v>1254.0271890579818</v>
+        <f t="shared" si="44"/>
+        <v>949.94990618435793</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="33"/>
-        <v>1265.3269003702062</v>
+        <f t="shared" si="44"/>
+        <v>955.47886615641767</v>
       </c>
       <c r="AI18" s="5">
-        <f t="shared" si="33"/>
-        <v>1276.6603011350842</v>
+        <f t="shared" si="44"/>
+        <v>960.91428102644693</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="33"/>
-        <v>1288.0245072004668</v>
+        <f t="shared" si="44"/>
+        <v>966.25015593179171</v>
       </c>
     </row>
     <row r="19" spans="2:148" x14ac:dyDescent="0.3">
@@ -2516,7 +2633,7 @@
         <v>633</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>53</v>
       </c>
       <c r="O19" s="5">
@@ -2527,6 +2644,13 @@
         <f>16+4</f>
         <v>20</v>
       </c>
+      <c r="Q19" s="5">
+        <f>-8+7</f>
+        <v>-1</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
       <c r="T19" s="5">
         <f>-29+21</f>
         <v>-8</v>
@@ -2551,48 +2675,48 @@
         <v>734</v>
       </c>
       <c r="Z19" s="5">
-        <f>Z17*0.02</f>
-        <v>107.88897799999997</v>
+        <f t="shared" si="43"/>
+        <v>24</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AJ19" si="34">AA17*0.02</f>
-        <v>117.82376534000001</v>
+        <f t="shared" ref="AA19:AJ19" si="45">AA17*0.02</f>
+        <v>93.615122599999978</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="34"/>
-        <v>123.95588095180005</v>
+        <f t="shared" si="45"/>
+        <v>97.197664512000017</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="34"/>
-        <v>129.20190674563599</v>
+        <f t="shared" si="45"/>
+        <v>100.55292752224</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="34"/>
-        <v>134.21506838541171</v>
+        <f t="shared" si="45"/>
+        <v>103.65094431067679</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="34"/>
-        <v>136.36239670958773</v>
+        <f t="shared" si="45"/>
+        <v>104.29269500238402</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="34"/>
-        <v>138.08487933775595</v>
+        <f t="shared" si="45"/>
+        <v>104.92590883472407</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="34"/>
-        <v>139.33635433977577</v>
+        <f t="shared" si="45"/>
+        <v>105.54998957603978</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="34"/>
-        <v>140.59187781891183</v>
+        <f t="shared" si="45"/>
+        <v>106.16431846182419</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="34"/>
-        <v>141.85114457056491</v>
+        <f t="shared" si="45"/>
+        <v>106.768253447383</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="34"/>
-        <v>143.11383413338521</v>
+        <f t="shared" si="45"/>
+        <v>107.36112843686576</v>
       </c>
     </row>
     <row r="20" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2608,544 +2732,552 @@
         <v>952</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" ref="K20:P20" si="35">K17-K18-K19</f>
+        <f t="shared" ref="K20:P20" si="46">K17-K18-K19</f>
         <v>735</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>894</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>564</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>938</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>851</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1026</v>
       </c>
+      <c r="Q20" s="8">
+        <f t="shared" ref="Q20:R20" si="47">Q17-Q18-Q19</f>
+        <v>792</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="47"/>
+        <v>711.67931199999998</v>
+      </c>
       <c r="T20" s="8">
-        <f t="shared" ref="T20:Z20" si="36">T17-T18-T19</f>
+        <f t="shared" ref="T20:Z20" si="48">T17-T18-T19</f>
         <v>893</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>958</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>1334</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>2530</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>3068</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>3131</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="36"/>
-        <v>4315.559119999999</v>
+        <f t="shared" si="48"/>
+        <v>3380.6793120000002</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" ref="AA20:AJ20" si="37">AA17-AA18-AA19</f>
-        <v>4712.9506136</v>
+        <f t="shared" ref="AA20:AJ20" si="49">AA17-AA18-AA19</f>
+        <v>3744.6049039999989</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="37"/>
-        <v>4958.2352380720022</v>
+        <f t="shared" si="49"/>
+        <v>3887.9065804800007</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="37"/>
-        <v>5168.0762698254402</v>
+        <f t="shared" si="49"/>
+        <v>4022.1171008895999</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="37"/>
-        <v>5368.6027354164689</v>
+        <f t="shared" si="49"/>
+        <v>4146.0377724270711</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="37"/>
-        <v>5454.4958683835102</v>
+        <f t="shared" si="49"/>
+        <v>4171.7078000953616</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="37"/>
-        <v>5523.3951735102382</v>
+        <f t="shared" si="49"/>
+        <v>4197.0363533889622</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="37"/>
-        <v>5573.4541735910316</v>
+        <f t="shared" si="49"/>
+        <v>4221.999583041591</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="37"/>
-        <v>5623.675112756473</v>
+        <f t="shared" si="49"/>
+        <v>4246.5727384729671</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="37"/>
-        <v>5674.0457828225963</v>
+        <f t="shared" si="49"/>
+        <v>4270.7301378953198</v>
       </c>
       <c r="AJ20" s="8">
-        <f t="shared" si="37"/>
-        <v>5724.5533653354078</v>
+        <f t="shared" si="49"/>
+        <v>4294.4451374746304</v>
       </c>
       <c r="AK20" s="1">
         <f>AJ20*(1+$AM$25)</f>
-        <v>5667.3078316820538</v>
+        <v>4251.5006860998838</v>
       </c>
       <c r="AL20" s="1">
-        <f t="shared" ref="AL20:CW20" si="38">AK20*(1+$AM$25)</f>
-        <v>5610.6347533652333</v>
+        <f t="shared" ref="AL20:CW20" si="50">AK20*(1+$AM$25)</f>
+        <v>4208.9856792388846</v>
       </c>
       <c r="AM20" s="1">
-        <f t="shared" si="38"/>
-        <v>5554.528405831581</v>
+        <f t="shared" si="50"/>
+        <v>4166.8958224464959</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="38"/>
-        <v>5498.9831217732653</v>
+        <f t="shared" si="50"/>
+        <v>4125.2268642220306</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="38"/>
-        <v>5443.9932905555324</v>
+        <f t="shared" si="50"/>
+        <v>4083.9745955798103</v>
       </c>
       <c r="AP20" s="1">
-        <f t="shared" si="38"/>
-        <v>5389.5533576499774</v>
+        <f t="shared" si="50"/>
+        <v>4043.1348496240121</v>
       </c>
       <c r="AQ20" s="1">
-        <f t="shared" si="38"/>
-        <v>5335.657824073478</v>
+        <f t="shared" si="50"/>
+        <v>4002.7035011277721</v>
       </c>
       <c r="AR20" s="1">
-        <f t="shared" si="38"/>
-        <v>5282.301245832743</v>
+        <f t="shared" si="50"/>
+        <v>3962.6764661164943</v>
       </c>
       <c r="AS20" s="1">
-        <f t="shared" si="38"/>
-        <v>5229.4782333744151</v>
+        <f t="shared" si="50"/>
+        <v>3923.0497014553293</v>
       </c>
       <c r="AT20" s="1">
-        <f t="shared" si="38"/>
-        <v>5177.1834510406707</v>
+        <f t="shared" si="50"/>
+        <v>3883.819204440776</v>
       </c>
       <c r="AU20" s="1">
-        <f t="shared" si="38"/>
-        <v>5125.4116165302639</v>
+        <f t="shared" si="50"/>
+        <v>3844.9810123963684</v>
       </c>
       <c r="AV20" s="1">
-        <f t="shared" si="38"/>
-        <v>5074.1575003649614</v>
+        <f t="shared" si="50"/>
+        <v>3806.5312022724047</v>
       </c>
       <c r="AW20" s="1">
-        <f t="shared" si="38"/>
-        <v>5023.4159253613116</v>
+        <f t="shared" si="50"/>
+        <v>3768.4658902496808</v>
       </c>
       <c r="AX20" s="1">
-        <f t="shared" si="38"/>
-        <v>4973.1817661076984</v>
+        <f t="shared" si="50"/>
+        <v>3730.7812313471841</v>
       </c>
       <c r="AY20" s="1">
-        <f t="shared" si="38"/>
-        <v>4923.4499484466214</v>
+        <f t="shared" si="50"/>
+        <v>3693.4734190337122</v>
       </c>
       <c r="AZ20" s="1">
-        <f t="shared" si="38"/>
-        <v>4874.2154489621553</v>
+        <f t="shared" si="50"/>
+        <v>3656.538684843375</v>
       </c>
       <c r="BA20" s="1">
-        <f t="shared" si="38"/>
-        <v>4825.4732944725338</v>
+        <f t="shared" si="50"/>
+        <v>3619.9732979949413</v>
       </c>
       <c r="BB20" s="1">
-        <f t="shared" si="38"/>
-        <v>4777.2185615278086</v>
+        <f t="shared" si="50"/>
+        <v>3583.7735650149916</v>
       </c>
       <c r="BC20" s="1">
-        <f t="shared" si="38"/>
-        <v>4729.4463759125301</v>
+        <f t="shared" si="50"/>
+        <v>3547.9358293648415</v>
       </c>
       <c r="BD20" s="1">
-        <f t="shared" si="38"/>
-        <v>4682.1519121534047</v>
+        <f t="shared" si="50"/>
+        <v>3512.4564710711929</v>
       </c>
       <c r="BE20" s="1">
-        <f t="shared" si="38"/>
-        <v>4635.3303930318707</v>
+        <f t="shared" si="50"/>
+        <v>3477.3319063604808</v>
       </c>
       <c r="BF20" s="1">
-        <f t="shared" si="38"/>
-        <v>4588.9770891015523</v>
+        <f t="shared" si="50"/>
+        <v>3442.5585872968759</v>
       </c>
       <c r="BG20" s="1">
-        <f t="shared" si="38"/>
-        <v>4543.087318210537</v>
+        <f t="shared" si="50"/>
+        <v>3408.133001423907</v>
       </c>
       <c r="BH20" s="1">
-        <f t="shared" si="38"/>
-        <v>4497.6564450284313</v>
+        <f t="shared" si="50"/>
+        <v>3374.051671409668</v>
       </c>
       <c r="BI20" s="1">
-        <f t="shared" si="38"/>
-        <v>4452.6798805781473</v>
+        <f t="shared" si="50"/>
+        <v>3340.3111546955711</v>
       </c>
       <c r="BJ20" s="1">
-        <f t="shared" si="38"/>
-        <v>4408.153081772366</v>
+        <f t="shared" si="50"/>
+        <v>3306.9080431486154</v>
       </c>
       <c r="BK20" s="1">
-        <f t="shared" si="38"/>
-        <v>4364.0715509546426</v>
+        <f t="shared" si="50"/>
+        <v>3273.8389627171291</v>
       </c>
       <c r="BL20" s="1">
-        <f t="shared" si="38"/>
-        <v>4320.4308354450959</v>
+        <f t="shared" si="50"/>
+        <v>3241.1005730899578</v>
       </c>
       <c r="BM20" s="1">
-        <f t="shared" si="38"/>
-        <v>4277.2265270906446</v>
+        <f t="shared" si="50"/>
+        <v>3208.6895673590584</v>
       </c>
       <c r="BN20" s="1">
-        <f t="shared" si="38"/>
-        <v>4234.4542618197383</v>
+        <f t="shared" si="50"/>
+        <v>3176.6026716854676</v>
       </c>
       <c r="BO20" s="1">
-        <f t="shared" si="38"/>
-        <v>4192.1097192015413</v>
+        <f t="shared" si="50"/>
+        <v>3144.8366449686127</v>
       </c>
       <c r="BP20" s="1">
-        <f t="shared" si="38"/>
-        <v>4150.1886220095257</v>
+        <f t="shared" si="50"/>
+        <v>3113.3882785189267</v>
       </c>
       <c r="BQ20" s="1">
-        <f t="shared" si="38"/>
-        <v>4108.6867357894307</v>
+        <f t="shared" si="50"/>
+        <v>3082.2543957337375</v>
       </c>
       <c r="BR20" s="1">
-        <f t="shared" si="38"/>
-        <v>4067.5998684315364</v>
+        <f t="shared" si="50"/>
+        <v>3051.4318517764</v>
       </c>
       <c r="BS20" s="1">
-        <f t="shared" si="38"/>
-        <v>4026.923869747221</v>
+        <f t="shared" si="50"/>
+        <v>3020.917533258636</v>
       </c>
       <c r="BT20" s="1">
-        <f t="shared" si="38"/>
-        <v>3986.6546310497488</v>
+        <f t="shared" si="50"/>
+        <v>2990.7083579260498</v>
       </c>
       <c r="BU20" s="1">
-        <f t="shared" si="38"/>
-        <v>3946.7880847392512</v>
+        <f t="shared" si="50"/>
+        <v>2960.8012743467893</v>
       </c>
       <c r="BV20" s="1">
-        <f t="shared" si="38"/>
-        <v>3907.3202038918585</v>
+        <f t="shared" si="50"/>
+        <v>2931.1932616033214</v>
       </c>
       <c r="BW20" s="1">
-        <f t="shared" si="38"/>
-        <v>3868.2470018529398</v>
+        <f t="shared" si="50"/>
+        <v>2901.8813289872883</v>
       </c>
       <c r="BX20" s="1">
-        <f t="shared" si="38"/>
-        <v>3829.5645318344104</v>
+        <f t="shared" si="50"/>
+        <v>2872.8625156974153</v>
       </c>
       <c r="BY20" s="1">
-        <f t="shared" si="38"/>
-        <v>3791.2688865160662</v>
+        <f t="shared" si="50"/>
+        <v>2844.1338905404414</v>
       </c>
       <c r="BZ20" s="1">
-        <f t="shared" si="38"/>
-        <v>3753.3561976509054</v>
+        <f t="shared" si="50"/>
+        <v>2815.692551635037</v>
       </c>
       <c r="CA20" s="1">
-        <f t="shared" si="38"/>
-        <v>3715.8226356743962</v>
+        <f t="shared" si="50"/>
+        <v>2787.5356261186867</v>
       </c>
       <c r="CB20" s="1">
-        <f t="shared" si="38"/>
-        <v>3678.6644093176524</v>
+        <f t="shared" si="50"/>
+        <v>2759.6602698574998</v>
       </c>
       <c r="CC20" s="1">
-        <f t="shared" si="38"/>
-        <v>3641.8777652244758</v>
+        <f t="shared" si="50"/>
+        <v>2732.0636671589245</v>
       </c>
       <c r="CD20" s="1">
-        <f t="shared" si="38"/>
-        <v>3605.4589875722309</v>
+        <f t="shared" si="50"/>
+        <v>2704.7430304873351</v>
       </c>
       <c r="CE20" s="1">
-        <f t="shared" si="38"/>
-        <v>3569.4043976965086</v>
+        <f t="shared" si="50"/>
+        <v>2677.6956001824619</v>
       </c>
       <c r="CF20" s="1">
-        <f t="shared" si="38"/>
-        <v>3533.7103537195435</v>
+        <f t="shared" si="50"/>
+        <v>2650.9186441806373</v>
       </c>
       <c r="CG20" s="1">
-        <f t="shared" si="38"/>
-        <v>3498.3732501823479</v>
+        <f t="shared" si="50"/>
+        <v>2624.409457738831</v>
       </c>
       <c r="CH20" s="1">
-        <f t="shared" si="38"/>
-        <v>3463.3895176805245</v>
+        <f t="shared" si="50"/>
+        <v>2598.1653631614427</v>
       </c>
       <c r="CI20" s="1">
-        <f t="shared" si="38"/>
-        <v>3428.7556225037192</v>
+        <f t="shared" si="50"/>
+        <v>2572.1837095298283</v>
       </c>
       <c r="CJ20" s="1">
-        <f t="shared" si="38"/>
-        <v>3394.4680662786818</v>
+        <f t="shared" si="50"/>
+        <v>2546.4618724345301</v>
       </c>
       <c r="CK20" s="1">
-        <f t="shared" si="38"/>
-        <v>3360.5233856158948</v>
+        <f t="shared" si="50"/>
+        <v>2520.9972537101849</v>
       </c>
       <c r="CL20" s="1">
-        <f t="shared" si="38"/>
-        <v>3326.9181517597358</v>
+        <f t="shared" si="50"/>
+        <v>2495.7872811730831</v>
       </c>
       <c r="CM20" s="1">
-        <f t="shared" si="38"/>
-        <v>3293.6489702421386</v>
+        <f t="shared" si="50"/>
+        <v>2470.8294083613523</v>
       </c>
       <c r="CN20" s="1">
-        <f t="shared" si="38"/>
-        <v>3260.712480539717</v>
+        <f t="shared" si="50"/>
+        <v>2446.1211142777388</v>
       </c>
       <c r="CO20" s="1">
-        <f t="shared" si="38"/>
-        <v>3228.1053557343198</v>
+        <f t="shared" si="50"/>
+        <v>2421.6599031349615</v>
       </c>
       <c r="CP20" s="1">
-        <f t="shared" si="38"/>
-        <v>3195.8243021769767</v>
+        <f t="shared" si="50"/>
+        <v>2397.4433041036118</v>
       </c>
       <c r="CQ20" s="1">
-        <f t="shared" si="38"/>
-        <v>3163.866059155207</v>
+        <f t="shared" si="50"/>
+        <v>2373.4688710625755</v>
       </c>
       <c r="CR20" s="1">
-        <f t="shared" si="38"/>
-        <v>3132.2273985636548</v>
+        <f t="shared" si="50"/>
+        <v>2349.7341823519496</v>
       </c>
       <c r="CS20" s="1">
-        <f t="shared" si="38"/>
-        <v>3100.9051245780183</v>
+        <f t="shared" si="50"/>
+        <v>2326.2368405284301</v>
       </c>
       <c r="CT20" s="1">
-        <f t="shared" si="38"/>
-        <v>3069.8960733322383</v>
+        <f t="shared" si="50"/>
+        <v>2302.9744721231459</v>
       </c>
       <c r="CU20" s="1">
-        <f t="shared" si="38"/>
-        <v>3039.1971125989157</v>
+        <f t="shared" si="50"/>
+        <v>2279.9447274019144</v>
       </c>
       <c r="CV20" s="1">
-        <f t="shared" si="38"/>
-        <v>3008.8051414729266</v>
+        <f t="shared" si="50"/>
+        <v>2257.1452801278951</v>
       </c>
       <c r="CW20" s="1">
-        <f t="shared" si="38"/>
-        <v>2978.7170900581973</v>
+        <f t="shared" si="50"/>
+        <v>2234.5738273266161</v>
       </c>
       <c r="CX20" s="1">
-        <f t="shared" ref="CX20:ER20" si="39">CW20*(1+$AM$25)</f>
-        <v>2948.9299191576151</v>
+        <f t="shared" ref="CX20:ER20" si="51">CW20*(1+$AM$25)</f>
+        <v>2212.2280890533498</v>
       </c>
       <c r="CY20" s="1">
-        <f t="shared" si="39"/>
-        <v>2919.4406199660389</v>
+        <f t="shared" si="51"/>
+        <v>2190.1058081628162</v>
       </c>
       <c r="CZ20" s="1">
-        <f t="shared" si="39"/>
-        <v>2890.2462137663783</v>
+        <f t="shared" si="51"/>
+        <v>2168.2047500811882</v>
       </c>
       <c r="DA20" s="1">
-        <f t="shared" si="39"/>
-        <v>2861.3437516287145</v>
+        <f t="shared" si="51"/>
+        <v>2146.5227025803765</v>
       </c>
       <c r="DB20" s="1">
-        <f t="shared" si="39"/>
-        <v>2832.7303141124271</v>
+        <f t="shared" si="51"/>
+        <v>2125.0574755545726</v>
       </c>
       <c r="DC20" s="1">
-        <f t="shared" si="39"/>
-        <v>2804.4030109713026</v>
+        <f t="shared" si="51"/>
+        <v>2103.8069007990271</v>
       </c>
       <c r="DD20" s="1">
-        <f t="shared" si="39"/>
-        <v>2776.3589808615893</v>
+        <f t="shared" si="51"/>
+        <v>2082.768831791037</v>
       </c>
       <c r="DE20" s="1">
-        <f t="shared" si="39"/>
-        <v>2748.5953910529734</v>
+        <f t="shared" si="51"/>
+        <v>2061.9411434731264</v>
       </c>
       <c r="DF20" s="1">
-        <f t="shared" si="39"/>
-        <v>2721.1094371424438</v>
+        <f t="shared" si="51"/>
+        <v>2041.3217320383951</v>
       </c>
       <c r="DG20" s="1">
-        <f t="shared" si="39"/>
-        <v>2693.8983427710191</v>
+        <f t="shared" si="51"/>
+        <v>2020.9085147180112</v>
       </c>
       <c r="DH20" s="1">
-        <f t="shared" si="39"/>
-        <v>2666.9593593433087</v>
+        <f t="shared" si="51"/>
+        <v>2000.6994295708312</v>
       </c>
       <c r="DI20" s="1">
-        <f t="shared" si="39"/>
-        <v>2640.2897657498756</v>
+        <f t="shared" si="51"/>
+        <v>1980.6924352751228</v>
       </c>
       <c r="DJ20" s="1">
-        <f t="shared" si="39"/>
-        <v>2613.886868092377</v>
+        <f t="shared" si="51"/>
+        <v>1960.8855109223716</v>
       </c>
       <c r="DK20" s="1">
-        <f t="shared" si="39"/>
-        <v>2587.7479994114533</v>
+        <f t="shared" si="51"/>
+        <v>1941.276655813148</v>
       </c>
       <c r="DL20" s="1">
-        <f t="shared" si="39"/>
-        <v>2561.8705194173385</v>
+        <f t="shared" si="51"/>
+        <v>1921.8638892550164</v>
       </c>
       <c r="DM20" s="1">
-        <f t="shared" si="39"/>
-        <v>2536.2518142231652</v>
+        <f t="shared" si="51"/>
+        <v>1902.6452503624662</v>
       </c>
       <c r="DN20" s="1">
-        <f t="shared" si="39"/>
-        <v>2510.8892960809335</v>
+        <f t="shared" si="51"/>
+        <v>1883.6187978588416</v>
       </c>
       <c r="DO20" s="1">
-        <f t="shared" si="39"/>
-        <v>2485.780403120124</v>
+        <f t="shared" si="51"/>
+        <v>1864.7826098802532</v>
       </c>
       <c r="DP20" s="1">
-        <f t="shared" si="39"/>
-        <v>2460.9225990889227</v>
+        <f t="shared" si="51"/>
+        <v>1846.1347837814506</v>
       </c>
       <c r="DQ20" s="1">
-        <f t="shared" si="39"/>
-        <v>2436.3133730980335</v>
+        <f t="shared" si="51"/>
+        <v>1827.6734359436359</v>
       </c>
       <c r="DR20" s="1">
-        <f t="shared" si="39"/>
-        <v>2411.9502393670532</v>
+        <f t="shared" si="51"/>
+        <v>1809.3967015841995</v>
       </c>
       <c r="DS20" s="1">
-        <f t="shared" si="39"/>
-        <v>2387.8307369733825</v>
+        <f t="shared" si="51"/>
+        <v>1791.3027345683574</v>
       </c>
       <c r="DT20" s="1">
-        <f t="shared" si="39"/>
-        <v>2363.9524296036489</v>
+        <f t="shared" si="51"/>
+        <v>1773.3897072226739</v>
       </c>
       <c r="DU20" s="1">
-        <f t="shared" si="39"/>
-        <v>2340.3129053076123</v>
+        <f t="shared" si="51"/>
+        <v>1755.6558101504472</v>
       </c>
       <c r="DV20" s="1">
-        <f t="shared" si="39"/>
-        <v>2316.9097762545362</v>
+        <f t="shared" si="51"/>
+        <v>1738.0992520489428</v>
       </c>
       <c r="DW20" s="1">
-        <f t="shared" si="39"/>
-        <v>2293.7406784919908</v>
+        <f t="shared" si="51"/>
+        <v>1720.7182595284535</v>
       </c>
       <c r="DX20" s="1">
-        <f t="shared" si="39"/>
-        <v>2270.803271707071</v>
+        <f t="shared" si="51"/>
+        <v>1703.5110769331689</v>
       </c>
       <c r="DY20" s="1">
-        <f t="shared" si="39"/>
-        <v>2248.0952389900003</v>
+        <f t="shared" si="51"/>
+        <v>1686.4759661638373</v>
       </c>
       <c r="DZ20" s="1">
-        <f t="shared" si="39"/>
-        <v>2225.6142866001005</v>
+        <f t="shared" si="51"/>
+        <v>1669.6112065021989</v>
       </c>
       <c r="EA20" s="1">
-        <f t="shared" si="39"/>
-        <v>2203.3581437340995</v>
+        <f t="shared" si="51"/>
+        <v>1652.915094437177</v>
       </c>
       <c r="EB20" s="1">
-        <f t="shared" si="39"/>
-        <v>2181.3245622967584</v>
+        <f t="shared" si="51"/>
+        <v>1636.3859434928052</v>
       </c>
       <c r="EC20" s="1">
-        <f t="shared" si="39"/>
-        <v>2159.5113166737906</v>
+        <f t="shared" si="51"/>
+        <v>1620.022084057877</v>
       </c>
       <c r="ED20" s="1">
-        <f t="shared" si="39"/>
-        <v>2137.9162035070526</v>
+        <f t="shared" si="51"/>
+        <v>1603.8218632172982</v>
       </c>
       <c r="EE20" s="1">
-        <f t="shared" si="39"/>
-        <v>2116.5370414719819</v>
+        <f t="shared" si="51"/>
+        <v>1587.7836445851251</v>
       </c>
       <c r="EF20" s="1">
-        <f t="shared" si="39"/>
-        <v>2095.3716710572621</v>
+        <f t="shared" si="51"/>
+        <v>1571.9058081392739</v>
       </c>
       <c r="EG20" s="1">
-        <f t="shared" si="39"/>
-        <v>2074.4179543466894</v>
+        <f t="shared" si="51"/>
+        <v>1556.186750057881</v>
       </c>
       <c r="EH20" s="1">
-        <f t="shared" si="39"/>
-        <v>2053.6737748032224</v>
+        <f t="shared" si="51"/>
+        <v>1540.6248825573023</v>
       </c>
       <c r="EI20" s="1">
-        <f t="shared" si="39"/>
-        <v>2033.1370370551901</v>
+        <f t="shared" si="51"/>
+        <v>1525.2186337317291</v>
       </c>
       <c r="EJ20" s="1">
-        <f t="shared" si="39"/>
-        <v>2012.8056666846383</v>
+        <f t="shared" si="51"/>
+        <v>1509.9664473944119</v>
       </c>
       <c r="EK20" s="1">
-        <f t="shared" si="39"/>
-        <v>1992.6776100177919</v>
+        <f t="shared" si="51"/>
+        <v>1494.8667829204678</v>
       </c>
       <c r="EL20" s="1">
-        <f t="shared" si="39"/>
-        <v>1972.750833917614</v>
+        <f t="shared" si="51"/>
+        <v>1479.9181150912632</v>
       </c>
       <c r="EM20" s="1">
-        <f t="shared" si="39"/>
-        <v>1953.0233255784378</v>
+        <f t="shared" si="51"/>
+        <v>1465.1189339403506</v>
       </c>
       <c r="EN20" s="1">
-        <f t="shared" si="39"/>
-        <v>1933.4930923226534</v>
+        <f t="shared" si="51"/>
+        <v>1450.4677446009471</v>
       </c>
       <c r="EO20" s="1">
-        <f t="shared" si="39"/>
-        <v>1914.1581613994269</v>
+        <f t="shared" si="51"/>
+        <v>1435.9630671549376</v>
       </c>
       <c r="EP20" s="1">
-        <f t="shared" si="39"/>
-        <v>1895.0165797854327</v>
+        <f t="shared" si="51"/>
+        <v>1421.6034364833881</v>
       </c>
       <c r="EQ20" s="1">
-        <f t="shared" si="39"/>
-        <v>1876.0664139875782</v>
+        <f t="shared" si="51"/>
+        <v>1407.3874021185543</v>
       </c>
       <c r="ER20" s="1">
-        <f t="shared" si="39"/>
-        <v>1857.3057498477024</v>
+        <f t="shared" si="51"/>
+        <v>1393.3135280973688</v>
       </c>
     </row>
     <row r="21" spans="2:148" x14ac:dyDescent="0.3">
@@ -3184,73 +3316,81 @@
         <f>552.7</f>
         <v>552.70000000000005</v>
       </c>
+      <c r="Q21" s="5">
+        <f>541.8</f>
+        <v>541.79999999999995</v>
+      </c>
+      <c r="R21" s="5">
+        <f>541.8</f>
+        <v>541.79999999999995</v>
+      </c>
       <c r="T21" s="5">
-        <f t="shared" ref="T21:Y21" si="40">554.4</f>
+        <f t="shared" ref="T21:Y21" si="52">554.4</f>
         <v>554.4</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>554.4</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>554.4</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>554.4</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>554.4</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>554.4</v>
       </c>
       <c r="Z21" s="5">
-        <f t="shared" ref="Z21:AJ21" si="41">552.7</f>
-        <v>552.70000000000005</v>
+        <f t="shared" ref="Z21:AJ21" si="53">541.8</f>
+        <v>541.79999999999995</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
       <c r="AJ21" s="5">
-        <f t="shared" si="41"/>
-        <v>552.70000000000005</v>
+        <f t="shared" si="53"/>
+        <v>541.79999999999995</v>
       </c>
     </row>
     <row r="22" spans="2:148" x14ac:dyDescent="0.3">
@@ -3266,96 +3406,104 @@
         <v>1.7171717171717173</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" ref="K22:P22" si="42">K20/K21</f>
+        <f t="shared" ref="K22:Q22" si="54">K20/K21</f>
         <v>1.3257575757575759</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>1.6125541125541125</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>1.0173160173160174</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>1.691919191919192</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>1.5349927849927851</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>1.8563415958024243</v>
       </c>
+      <c r="Q22" s="7">
+        <f t="shared" si="54"/>
+        <v>1.4617940199335548</v>
+      </c>
+      <c r="R22" s="7">
+        <f t="shared" ref="R22" si="55">R20/R21</f>
+        <v>1.3135461646363973</v>
+      </c>
       <c r="T22" s="7">
-        <f t="shared" ref="T22:Z22" si="43">T20/T21</f>
+        <f t="shared" ref="T22:Z22" si="56">T20/T21</f>
         <v>1.6107503607503608</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="56"/>
         <v>1.727994227994228</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="56"/>
         <v>2.4062049062049065</v>
       </c>
       <c r="W22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="56"/>
         <v>4.5634920634920633</v>
       </c>
       <c r="X22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="56"/>
         <v>5.5339105339105341</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="56"/>
         <v>5.6475468975468974</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" si="43"/>
-        <v>7.8081402569205691</v>
+        <f t="shared" si="56"/>
+        <v>6.2397181838316733</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AJ22" si="44">AA20/AA21</f>
-        <v>8.5271406072010123</v>
+        <f t="shared" ref="AA22:AJ22" si="57">AA20/AA21</f>
+        <v>6.9114154743447749</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="44"/>
-        <v>8.9709340294409294</v>
+        <f t="shared" si="57"/>
+        <v>7.1759073098560373</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" si="44"/>
-        <v>9.3505993664292379</v>
+        <f t="shared" si="57"/>
+        <v>7.4236196029708381</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" si="44"/>
-        <v>9.7134118607137125</v>
+        <f t="shared" si="57"/>
+        <v>7.6523399269602645</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="44"/>
-        <v>9.8688182890962732</v>
+        <f t="shared" si="57"/>
+        <v>7.6997190847090478</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" si="44"/>
-        <v>9.9934777881495158</v>
+        <f t="shared" si="57"/>
+        <v>7.7464679833683325</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" si="44"/>
-        <v>10.084049527032805</v>
+        <f t="shared" si="57"/>
+        <v>7.792542604358788</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="44"/>
-        <v>10.174914262269716</v>
+        <f t="shared" si="57"/>
+        <v>7.8378972655462666</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="44"/>
-        <v>10.266049905595432</v>
+        <f t="shared" si="57"/>
+        <v>7.8824845660674052</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="44"/>
-        <v>10.357433264583694</v>
+        <f t="shared" si="57"/>
+        <v>7.92625532941054</v>
       </c>
     </row>
     <row r="24" spans="2:148" x14ac:dyDescent="0.3">
@@ -3367,11 +3515,11 @@
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
-        <f t="shared" ref="L24:M26" si="45">L3/H3-1</f>
+        <f t="shared" ref="L24:M26" si="58">L3/H3-1</f>
         <v>5.504587155963292E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>5.7135728542914155E-2</v>
       </c>
       <c r="N24" s="9"/>
@@ -3380,32 +3528,32 @@
         <v>1.1249999999999982E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24:P26" si="46">P3/L3-1</f>
+        <f t="shared" ref="P24:P26" si="59">P3/L3-1</f>
         <v>3.9613526570048352E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:Q26" si="47">Q3/M3-1</f>
-        <v>-1</v>
+        <f t="shared" ref="Q24:Q26" si="60">Q3/M3-1</f>
+        <v>8.4965777672880716E-3</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24:R26" si="48">R3/N3-1</f>
-        <v>-1</v>
+        <f t="shared" ref="R24:R26" si="61">R3/N3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:X24" si="49">U3/T3-1</f>
+        <f t="shared" ref="U24:X24" si="62">U3/T3-1</f>
         <v>0.42482211594540997</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="62"/>
         <v>8.9398280802292174E-2</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="62"/>
         <v>8.6646126099045651E-2</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="62"/>
         <v>8.0912863070539354E-2</v>
       </c>
       <c r="Y24" s="9">
@@ -3413,47 +3561,47 @@
         <v>6.4427383237364078E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AJ24" si="50">Z3/Y3-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="Z24:AJ24" si="63">Z3/Y3-1</f>
+        <v>1.984732824427482E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3466,93 +3614,93 @@
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>0.16225961538461542</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>0.13063583815028901</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:O26" si="51">O4/K4-1</f>
+        <f t="shared" ref="O25:O26" si="64">O4/K4-1</f>
         <v>0.22876557191392988</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="59"/>
         <v>0.25336091003102368</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="47"/>
-        <v>-1</v>
+        <f t="shared" si="60"/>
+        <v>1.2269938650306678E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="48"/>
-        <v>-1</v>
+        <f t="shared" si="61"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9">
-        <f t="shared" ref="U25:X25" si="52">U4/T4-1</f>
+        <f t="shared" ref="U25:X25" si="65">U4/T4-1</f>
         <v>0.63382899628252787</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="65"/>
         <v>0.10693970420932875</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="65"/>
         <v>0.12264474134977732</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="65"/>
         <v>5.675923100396707E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" ref="Y25:AJ26" si="53">Y4/X4-1</f>
+        <f t="shared" ref="Y25:AJ26" si="66">Y4/X4-1</f>
         <v>0.10280103956107411</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="53"/>
-        <v>0.25</v>
+        <f t="shared" si="66"/>
+        <v>0.12537837130138763</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="53"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="66"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="53"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="66"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="53"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="53"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="53"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="53"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" t="s">
@@ -3571,94 +3719,94 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>7.3801513877207681E-2</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>7.0182639031397542E-2</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="64"/>
         <v>5.058365758754868E-2</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="59"/>
         <v>8.0086156256119034E-2</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="47"/>
-        <v>-1</v>
+        <f t="shared" si="60"/>
+        <v>9.2042186001917159E-3</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="48"/>
-        <v>-1</v>
+        <f t="shared" si="61"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10">
-        <f t="shared" ref="U26:X26" si="54">U5/T5-1</f>
+        <f t="shared" ref="U26:X26" si="67">U5/T5-1</f>
         <v>0.45793658584470398</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>9.2512792889846596E-2</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>9.3122149636386098E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>7.6450358008682384E-2</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="66"/>
         <v>7.1387419473105229E-2</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="53"/>
-        <v>7.9205612045365692E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.9549276495893571E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="53"/>
-        <v>5.5948724034855735E-2</v>
+        <f t="shared" si="66"/>
+        <v>3.4042149972113744E-2</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="53"/>
-        <v>3.6484956744428532E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.4104530430248072E-2</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="53"/>
-        <v>2.9906340647923191E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.2084119111192901E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="53"/>
-        <v>2.764685147014867E-2</v>
+        <f t="shared" si="66"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.7813184103244728E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2100260286203701E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.5322333275749944E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2116653434435465E-2</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.2699636900695532E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2133139985196273E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.2719098080390845E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2149719932035952E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.2738646923175168E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2166393259313457E-2</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="53"/>
-        <v>1.2758283067527243E-2</v>
+        <f t="shared" si="66"/>
+        <v>1.2183159942096067E-2</v>
       </c>
       <c r="AL26" t="s">
         <v>56</v>
@@ -3672,28 +3820,28 @@
         <v>49</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N28" si="55">(H3-H6)/H3</f>
+        <f t="shared" ref="H27:N28" si="68">(H3-H6)/H3</f>
         <v>0.65570846075433231</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.67290419161676651</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.66149999999999998</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.67560386473429956</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.68232239792305882</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.6901408450704225</v>
       </c>
       <c r="O27" s="9">
@@ -3701,91 +3849,91 @@
         <v>0.6566131025957973</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:R27" si="56">(P3-P6)/P3</f>
+        <f t="shared" ref="P27:R27" si="69">(P3-P6)/P3</f>
         <v>0.67193308550185871</v>
       </c>
-      <c r="Q27" s="9" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R27" s="9" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
+      <c r="Q27" s="9">
+        <f t="shared" si="69"/>
+        <v>0.65223496372571965</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="69"/>
+        <v>0.66</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:X27" si="57">(T3-T6)/T3</f>
+        <f t="shared" ref="T27:X27" si="70">(T3-T6)/T3</f>
         <v>0.53155254869940516</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0.52181743757674992</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0.54279702412264219</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0.60089903181189486</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="70"/>
         <v>0.65886116442738318</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27:Y28" si="58">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y27:Y28" si="71">(Y3-Y6)/Y3</f>
         <v>0.67764621025425253</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AJ27" si="59">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z27:AJ27" si="72">(Z3-Z6)/Z3</f>
+        <v>0.66026403885143103</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.68</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.68</v>
+      </c>
+      <c r="AC27" s="9">
+        <f t="shared" si="72"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="AA27" s="9">
-        <f t="shared" si="59"/>
+      <c r="AD27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.68</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.68</v>
+      </c>
+      <c r="AF27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.68</v>
+      </c>
+      <c r="AG27" s="9">
+        <f t="shared" si="72"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="59"/>
+      <c r="AH27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="AI27" s="9">
+        <f t="shared" si="72"/>
         <v>0.68</v>
       </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="59"/>
+      <c r="AJ27" s="9">
+        <f t="shared" si="72"/>
         <v>0.67999999999999994</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
-      </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="59"/>
-        <v>0.68</v>
       </c>
       <c r="AL27" t="s">
         <v>57</v>
       </c>
       <c r="AM27" s="5">
         <f>NPV(AM26,Z20:ER20)</f>
-        <v>72599.222768261767</v>
+        <v>55244.300247948791</v>
       </c>
     </row>
     <row r="28" spans="2:148" x14ac:dyDescent="0.3">
@@ -3793,113 +3941,113 @@
         <v>50</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.30528846153846156</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.32601156069364162</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.26274065685164211</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.3391933815925543</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.32413087934560325</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="68"/>
         <v>0.29465186680121092</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:P28" si="60">(O4-O7)/O4</f>
+        <f t="shared" ref="O28:P28" si="73">(O4-O7)/O4</f>
         <v>0.36958525345622117</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="73"/>
         <v>0.4273927392739274</v>
       </c>
-      <c r="Q28" s="9" t="e">
-        <f t="shared" ref="Q28:R28" si="61">(Q4-Q7)/Q4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R28" s="9" t="e">
-        <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+      <c r="Q28" s="9">
+        <f t="shared" ref="Q28:R28" si="74">(Q4-Q7)/Q4</f>
+        <v>0.31414141414141417</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="74"/>
+        <v>0.28000000000000008</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:X28" si="62">(T4-T7)/T4</f>
+        <f t="shared" ref="T28:X28" si="75">(T4-T7)/T4</f>
         <v>0.19888475836431227</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="75"/>
         <v>0.25255972696245732</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="75"/>
         <v>0.29976019184652281</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="75"/>
         <v>0.32224595666768385</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="75"/>
         <v>0.32486283569159691</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="71"/>
         <v>0.30610107357947108</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AJ28" si="63">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z28:AJ28" si="76">(Z4-Z7)/Z4</f>
+        <v>0.35204582788483463</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AC28" s="9">
+        <f t="shared" si="76"/>
         <v>0.35</v>
       </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AD28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AF28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AG28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AH28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AI28" s="9">
+        <f t="shared" si="76"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="AJ28" s="9">
+        <f t="shared" si="76"/>
         <v>0.35</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35</v>
-      </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.34999999999999992</v>
-      </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.34999999999999992</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.34999999999999992</v>
-      </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35</v>
-      </c>
-      <c r="AI28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35</v>
-      </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.35000000000000003</v>
       </c>
       <c r="AL28" t="s">
         <v>58</v>
@@ -3914,28 +4062,28 @@
         <v>51</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:N29" si="64">H9/H5</f>
+        <f t="shared" ref="H29:N29" si="77">H9/H5</f>
         <v>0.59440706476030281</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="77"/>
         <v>0.6113277241945414</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="77"/>
         <v>0.58939176735613352</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="77"/>
         <v>0.61190522811826908</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="77"/>
         <v>0.61514860977948227</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="77"/>
         <v>0.61550180917920394</v>
       </c>
       <c r="O29" s="9">
@@ -3943,91 +4091,91 @@
         <v>0.59590643274853805</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29:R29" si="65">P9/P5</f>
+        <f t="shared" ref="P29:R29" si="78">P9/P5</f>
         <v>0.6182015953589558</v>
       </c>
-      <c r="Q29" s="9" t="e">
-        <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R29" s="9" t="e">
-        <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
+      <c r="Q29" s="9">
+        <f t="shared" si="78"/>
+        <v>0.58863765912977384</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" si="78"/>
+        <v>0.58828413635498</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29:X29" si="66">T9/T5</f>
+        <f t="shared" ref="T29:X29" si="79">T9/T5</f>
         <v>0.47884558751349759</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="79"/>
         <v>0.47401023431187717</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="79"/>
         <v>0.4990755577468261</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="79"/>
         <v>0.54941647403732308</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="79"/>
         <v>0.59828209291363332</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="67">Y9/Y5</f>
+        <f t="shared" ref="Y29" si="80">Y9/Y5</f>
         <v>0.60828118889323424</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AJ29" si="68">Z9/Z5</f>
-        <v>0.60864100890414707</v>
+        <f t="shared" ref="Z29:AJ29" si="81">Z9/Z5</f>
+        <v>0.5979708272082509</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.60228520391912321</v>
+        <f t="shared" si="81"/>
+        <v>0.61227524790090937</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.59827268965463354</v>
+        <f t="shared" si="81"/>
+        <v>0.61122406933063411</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.59588463382836521</v>
+        <f t="shared" si="81"/>
+        <v>0.61069141055527909</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.59405497486430814</v>
+        <f t="shared" si="81"/>
+        <v>0.61069141055527909</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.59218150095012645</v>
+        <f t="shared" si="81"/>
+        <v>0.61015043666363245</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.5909119822770571</v>
+        <f t="shared" si="81"/>
+        <v>0.60960638048852112</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.59026976334710357</v>
+        <f t="shared" si="81"/>
+        <v>0.60905924224281538</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.58962465153521859</v>
+        <f t="shared" si="81"/>
+        <v>0.60850902244266081</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.58897665877159933</v>
+        <f t="shared" si="81"/>
+        <v>0.60795572191083025</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.58832579737412216</v>
+        <f t="shared" si="81"/>
+        <v>0.60739934178004207</v>
       </c>
       <c r="AL29" t="s">
         <v>59</v>
       </c>
       <c r="AM29" s="5">
         <f>AM27+AM28</f>
-        <v>44011.222768261767</v>
+        <v>26656.300247948791</v>
       </c>
     </row>
     <row r="30" spans="2:148" x14ac:dyDescent="0.3">
@@ -4039,11 +4187,11 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:M30" si="69">L10/H10-1</f>
+        <f t="shared" ref="L30:M30" si="82">L10/H10-1</f>
         <v>5.8962264150941301E-4</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="82"/>
         <v>-2.7845036319612548E-2</v>
       </c>
       <c r="N30" s="9"/>
@@ -4052,32 +4200,32 @@
         <v>-8.8391278727165679E-3</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30" si="70">P10/L10-1</f>
+        <f t="shared" ref="P30" si="83">P10/L10-1</f>
         <v>8.2498526812020412E-3</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30" si="71">Q10/M10-1</f>
-        <v>-1</v>
+        <f t="shared" ref="Q30" si="84">Q10/M10-1</f>
+        <v>9.7135740971357354E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" ref="R30" si="72">R10/N10-1</f>
-        <v>-1</v>
+        <f t="shared" ref="R30" si="85">R10/N10-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="T30" s="9"/>
       <c r="U30" s="9">
-        <f t="shared" ref="U30:X30" si="73">U10/T10-1</f>
+        <f t="shared" ref="U30:X30" si="86">U10/T10-1</f>
         <v>0.72107186358099873</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="86"/>
         <v>2.7954706298655374E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="86"/>
         <v>4.2857142857142927E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="86"/>
         <v>8.5327611817131555E-2</v>
       </c>
       <c r="Y30" s="9">
@@ -4085,47 +4233,47 @@
         <v>-1.8248175182481452E-3</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AJ30" si="74">Z10/Y10-1</f>
+        <f t="shared" ref="Z30:AJ30" si="87">Z10/Y10-1</f>
+        <v>5.6971358927483173E-2</v>
+      </c>
+      <c r="AA30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AB30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AB30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AC30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AD30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AE30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AF30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AG30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AH30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="74"/>
+      <c r="AI30" s="9">
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI30" s="9">
-        <f t="shared" si="74"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL30" t="s">
@@ -4133,7 +4281,7 @@
       </c>
       <c r="AM30" s="4">
         <f>AM29/AJ21</f>
-        <v>79.629496595371378</v>
+        <v>49.199520575763742</v>
       </c>
     </row>
     <row r="31" spans="2:148" x14ac:dyDescent="0.3">
@@ -4141,28 +4289,28 @@
         <v>53</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:N31" si="75">H13/H5</f>
+        <f t="shared" ref="H31:N31" si="88">H13/H5</f>
         <v>0.23780487804878048</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>0.30843422942745741</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>0.24185951259471636</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>0.27961621304092421</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>0.30719079578139979</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>0.3176537802323367</v>
       </c>
       <c r="O31" s="9">
@@ -4170,91 +4318,91 @@
         <v>0.27192982456140352</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" ref="P31:R31" si="76">P13/P5</f>
+        <f t="shared" ref="P31:R31" si="89">P13/P5</f>
         <v>0.30746918056562728</v>
       </c>
-      <c r="Q31" s="9" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R31" s="9" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
+      <c r="Q31" s="9">
+        <f t="shared" si="89"/>
+        <v>0.27284818544556338</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="89"/>
+        <v>0.25539516282612834</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:X31" si="77">T13/T5</f>
+        <f t="shared" ref="T31:X31" si="90">T13/T5</f>
         <v>0.15794640227741238</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>0.12469701050363588</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>0.14100825835079503</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>0.21085865704459605</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>0.26260933326349972</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="78">Y13/Y5</f>
+        <f t="shared" ref="Y31" si="91">Y13/Y5</f>
         <v>0.28739734063355493</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31:AJ31" si="79">Z13/Z5</f>
-        <v>0.30833429892694536</v>
+        <f t="shared" ref="Z31:AJ31" si="92">Z13/Z5</f>
+        <v>0.27721119472260081</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.31504608882458968</v>
+        <f t="shared" si="92"/>
+        <v>0.29359941619707042</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.31837330051471646</v>
+        <f t="shared" si="92"/>
+        <v>0.29693721632193193</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32139522457444397</v>
+        <f t="shared" si="92"/>
+        <v>0.30012037672019032</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32427912438624762</v>
+        <f t="shared" si="92"/>
+        <v>0.30316519077739706</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32447656920186363</v>
+        <f t="shared" si="92"/>
+        <v>0.30326238005170308</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32461036336810634</v>
+        <f t="shared" si="92"/>
+        <v>0.30336012307711935</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.3246780466153884</v>
+        <f t="shared" si="92"/>
+        <v>0.3034584198154025</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32474603474257036</v>
+        <f t="shared" si="92"/>
+        <v>0.30355727017382378</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32481432649233249</v>
+        <f t="shared" si="92"/>
+        <v>0.30365667400456703</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="79"/>
-        <v>0.32488292056649809</v>
+        <f t="shared" si="92"/>
+        <v>0.30375663110413242</v>
       </c>
       <c r="AL31" t="s">
         <v>61</v>
       </c>
       <c r="AM31" s="4">
         <f>Main!D3</f>
-        <v>125.45</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="32" spans="2:148" x14ac:dyDescent="0.3">
@@ -4262,28 +4410,28 @@
         <v>27</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:N32" si="80">H18/H17</f>
+        <f t="shared" ref="H32:N32" si="93">H18/H17</f>
         <v>0.20733104238258879</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="93"/>
         <v>0.1975206611570248</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="93"/>
         <v>0.16757940854326397</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="93"/>
         <v>0.19420035149384884</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="93"/>
         <v>5.8221872541306056E-2</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="93"/>
         <v>0.16300675675675674</v>
       </c>
       <c r="O32" s="9">
@@ -4291,83 +4439,83 @@
         <v>0.18164435946462715</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" ref="P32:R32" si="81">P18/P17</f>
+        <f t="shared" ref="P32:R32" si="94">P18/P17</f>
         <v>0.19040247678018576</v>
       </c>
-      <c r="Q32" s="9" t="e">
-        <f t="shared" si="81"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R32" s="9" t="e">
-        <f t="shared" si="81"/>
-        <v>#DIV/0!</v>
+      <c r="Q32" s="9">
+        <f t="shared" si="94"/>
+        <v>0.17946058091286307</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="94"/>
+        <v>0.18000000000000002</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" ref="T32:X32" si="82">T18/T17</f>
+        <f t="shared" ref="T32:X32" si="95">T18/T17</f>
         <v>0.18282548476454294</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="95"/>
         <v>0.16737830913748933</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="95"/>
         <v>0.21788715486194477</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="95"/>
         <v>0.1891520768966701</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="95"/>
         <v>0.19343252950230888</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32" si="83">Y18/Y17</f>
+        <f t="shared" ref="Y32" si="96">Y18/Y17</f>
         <v>0.14225477141588994</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" ref="Z32:AJ32" si="84">Z18/Z17</f>
+        <f t="shared" ref="Z32:AJ32" si="97">Z18/Z17</f>
+        <v>0.18351087421343465</v>
+      </c>
+      <c r="AA32" s="9">
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="84"/>
+      <c r="AB32" s="9">
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="84"/>
-        <v>0.17999999999999997</v>
-      </c>
       <c r="AC32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="84"/>
-        <v>0.17999999999999997</v>
+        <f t="shared" si="97"/>
+        <v>0.18</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="84"/>
-        <v>0.17999999999999997</v>
+        <f t="shared" si="97"/>
+        <v>0.18</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="97"/>
         <v>0.18</v>
       </c>
       <c r="AL32" s="1" t="s">
@@ -4375,7 +4523,7 @@
       </c>
       <c r="AM32" s="10">
         <f>AM30/AM31-1</f>
-        <v>-0.36524913036770523</v>
+        <v>-0.30213445991824484</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
@@ -4383,28 +4531,28 @@
         <v>54</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:N33" si="85">H20/H5</f>
+        <f t="shared" ref="H33:N33" si="98">H20/H5</f>
         <v>0.14360807401177461</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="98"/>
         <v>0.19536219987687256</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="98"/>
         <v>0.15052221994675405</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="98"/>
         <v>0.1750538476600744</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="98"/>
         <v>0.10814956855225312</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="98"/>
         <v>0.17863264140163779</v>
       </c>
       <c r="O33" s="9">
@@ -4412,90 +4560,90 @@
         <v>0.16588693957115011</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" ref="P33:R33" si="86">P20/P5</f>
+        <f t="shared" ref="P33:R33" si="99">P20/P5</f>
         <v>0.18600435097897028</v>
       </c>
-      <c r="Q33" s="9" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R33" s="9" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
+      <c r="Q33" s="9">
+        <f t="shared" si="99"/>
+        <v>0.15048451453543607</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="99"/>
+        <v>0.13287465543444574</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" ref="T33:X33" si="87">T20/T5</f>
+        <f t="shared" ref="T33:X33" si="100">T20/T5</f>
         <v>8.766074408559929E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="100"/>
         <v>6.4503097225962827E-2</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="100"/>
         <v>8.2213731048933814E-2</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="100"/>
         <v>0.14263967976546202</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="100"/>
         <v>0.1606871628345467</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33" si="88">Y20/Y5</f>
+        <f t="shared" ref="Y33" si="101">Y20/Y5</f>
         <v>0.15306022682831444</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" ref="Z33:AJ33" si="89">Z20/Z5</f>
-        <v>0.1954844246504045</v>
+        <f t="shared" ref="Z33:AJ33" si="102">Z20/Z5</f>
+        <v>0.1589784214639817</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.2021739280162074</v>
+        <f t="shared" si="102"/>
+        <v>0.17029502640124272</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20520899076042073</v>
+        <f t="shared" si="102"/>
+        <v>0.17265036315691701</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20768275646369294</v>
+        <f t="shared" si="102"/>
+        <v>0.17475103046652715</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20993695675411811</v>
+        <f t="shared" si="102"/>
+        <v>0.17660301652358787</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20956279109037529</v>
+        <f t="shared" si="102"/>
+        <v>0.17557198040178582</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20900743421653811</v>
+        <f t="shared" si="102"/>
+        <v>0.17452332823309177</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20825689935963879</v>
+        <f t="shared" si="102"/>
+        <v>0.17345678663753358</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20749430741328945</v>
+        <f t="shared" si="102"/>
+        <v>0.17237207858300005</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20671948569222967</v>
+        <f t="shared" si="102"/>
+        <v>0.17126892334864793</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="89"/>
-        <v>0.20593225946595745</v>
+        <f t="shared" si="102"/>
+        <v>0.17014703648816909</v>
       </c>
       <c r="AL33" t="s">
         <v>63</v>
       </c>
       <c r="AM33" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
